--- a/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_105.xlsx
+++ b/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_105.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="AB1" s="2" t="inlineStr">
         <is>
-          <t>ev cases</t>
+          <t>nv cases</t>
         </is>
       </c>
       <c r="AC1" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
         <v>35664</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0</v>
+        <v>29116</v>
       </c>
       <c r="AC2" s="3" t="n">
         <v>1477017</v>
@@ -859,16 +859,16 @@
         <v>0.019464</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" s="3" t="n">
         <v>34035</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0</v>
+        <v>7880</v>
       </c>
       <c r="AC3" s="3" t="n">
         <v>736525</v>
@@ -1013,7 +1013,7 @@
         <v>27918</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>0</v>
+        <v>11726</v>
       </c>
       <c r="AC4" s="3" t="n">
         <v>828151</v>
@@ -1158,7 +1158,7 @@
         <v>8482</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>0</v>
+        <v>4477</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>549016</v>
@@ -1303,7 +1303,7 @@
         <v>6805</v>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>0</v>
+        <v>3551</v>
       </c>
       <c r="AC6" s="3" t="n">
         <v>341931</v>
@@ -1444,7 +1444,7 @@
         <v>7677</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>0</v>
+        <v>1465</v>
       </c>
       <c r="AC7" s="3" t="n">
         <v>263686</v>
@@ -1585,7 +1585,7 @@
         <v>8532</v>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>0</v>
+        <v>4129</v>
       </c>
       <c r="AC8" s="3" t="n">
         <v>522328</v>
@@ -1726,7 +1726,7 @@
         <v>25337</v>
       </c>
       <c r="AB9" s="3" t="n">
-        <v>67</v>
+        <v>4683</v>
       </c>
       <c r="AC9" s="3" t="n">
         <v>293090</v>
@@ -1858,16 +1858,16 @@
         <v>0.007346</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" s="3" t="n">
         <v>6490</v>
       </c>
       <c r="AB10" s="3" t="n">
-        <v>0</v>
+        <v>2130</v>
       </c>
       <c r="AC10" s="3" t="n">
         <v>258750</v>
@@ -2012,7 +2012,7 @@
         <v>1462</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>0</v>
+        <v>2601</v>
       </c>
       <c r="AC11" s="3" t="n">
         <v>255121</v>
@@ -2151,13 +2151,13 @@
         <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="3" t="n">
         <v>7136</v>
       </c>
       <c r="AB12" s="3" t="n">
-        <v>0</v>
+        <v>2405</v>
       </c>
       <c r="AC12" s="3" t="n">
         <v>254011</v>
@@ -2302,7 +2302,7 @@
         <v>13685</v>
       </c>
       <c r="AB13" s="3" t="n">
-        <v>38</v>
+        <v>4154</v>
       </c>
       <c r="AC13" s="3" t="n">
         <v>289842</v>
@@ -2437,7 +2437,7 @@
         <v>4465</v>
       </c>
       <c r="AB14" s="3" t="n">
-        <v>0</v>
+        <v>2941</v>
       </c>
       <c r="AC14" s="3" t="n">
         <v>284086</v>
@@ -2557,7 +2557,7 @@
         <v>1620</v>
       </c>
       <c r="AB15" s="3" t="n">
-        <v>0</v>
+        <v>2624</v>
       </c>
       <c r="AC15" s="3" t="n">
         <v>157291</v>
@@ -2677,7 +2677,7 @@
         <v>4207</v>
       </c>
       <c r="AB16" s="3" t="n">
-        <v>0</v>
+        <v>1959</v>
       </c>
       <c r="AC16" s="3" t="n">
         <v>247527</v>
@@ -2788,16 +2788,16 @@
         <v>0.004867</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" s="3" t="n">
         <v>6813</v>
       </c>
       <c r="AB17" s="3" t="n">
-        <v>0</v>
+        <v>2250</v>
       </c>
       <c r="AC17" s="3" t="n">
         <v>238986</v>
@@ -2917,7 +2917,7 @@
         <v>2380</v>
       </c>
       <c r="AB18" s="3" t="n">
-        <v>0</v>
+        <v>2684</v>
       </c>
       <c r="AC18" s="3" t="n">
         <v>267206</v>
@@ -3028,16 +3028,16 @@
         <v>0.005427</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="3" t="n">
         <v>1918</v>
       </c>
       <c r="AB19" s="3" t="n">
-        <v>0</v>
+        <v>2683</v>
       </c>
       <c r="AC19" s="3" t="n">
         <v>235685</v>
@@ -3157,7 +3157,7 @@
         <v>4952</v>
       </c>
       <c r="AB20" s="3" t="n">
-        <v>0</v>
+        <v>3407</v>
       </c>
       <c r="AC20" s="3" t="n">
         <v>269074</v>
@@ -3277,7 +3277,7 @@
         <v>4867</v>
       </c>
       <c r="AB21" s="3" t="n">
-        <v>0</v>
+        <v>4657</v>
       </c>
       <c r="AC21" s="3" t="n">
         <v>211676</v>
@@ -3388,16 +3388,16 @@
         <v>0.004167</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="n">
         <v>3606</v>
       </c>
       <c r="AB22" s="3" t="n">
-        <v>0</v>
+        <v>2623</v>
       </c>
       <c r="AC22" s="3" t="n">
         <v>215076</v>
@@ -3508,16 +3508,16 @@
         <v>0.004559</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="3" t="n">
         <v>4123</v>
       </c>
       <c r="AB23" s="3" t="n">
-        <v>0</v>
+        <v>1742</v>
       </c>
       <c r="AC23" s="3" t="n">
         <v>214509</v>
@@ -3628,7 +3628,7 @@
         <v>0.005151</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>0</v>
@@ -3637,7 +3637,7 @@
         <v>3006</v>
       </c>
       <c r="AB24" s="3" t="n">
-        <v>0</v>
+        <v>2215</v>
       </c>
       <c r="AC24" s="3" t="n">
         <v>139375</v>
@@ -3757,7 +3757,7 @@
         <v>1432</v>
       </c>
       <c r="AB25" s="3" t="n">
-        <v>0</v>
+        <v>1468</v>
       </c>
       <c r="AC25" s="3" t="n">
         <v>147675</v>
@@ -3877,7 +3877,7 @@
         <v>2262</v>
       </c>
       <c r="AB26" s="3" t="n">
-        <v>0</v>
+        <v>3157</v>
       </c>
       <c r="AC26" s="3" t="n">
         <v>262194</v>
@@ -3988,16 +3988,16 @@
         <v>0.004224</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA27" s="3" t="n">
         <v>3369</v>
       </c>
       <c r="AB27" s="3" t="n">
-        <v>0</v>
+        <v>3996</v>
       </c>
       <c r="AC27" s="3" t="n">
         <v>254023</v>
@@ -4117,7 +4117,7 @@
         <v>2908</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>0</v>
+        <v>2603</v>
       </c>
       <c r="AC28" s="3" t="n">
         <v>159960</v>
@@ -4237,7 +4237,7 @@
         <v>3797</v>
       </c>
       <c r="AB29" s="3" t="n">
-        <v>0</v>
+        <v>3769</v>
       </c>
       <c r="AC29" s="3" t="n">
         <v>83977</v>
@@ -4357,7 +4357,7 @@
         <v>3860</v>
       </c>
       <c r="AB30" s="3" t="n">
-        <v>0</v>
+        <v>1551</v>
       </c>
       <c r="AC30" s="3" t="n">
         <v>200571</v>
@@ -4468,16 +4468,16 @@
         <v>0.004758</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="3" t="n">
         <v>2551</v>
       </c>
       <c r="AB31" s="3" t="n">
-        <v>0</v>
+        <v>1131</v>
       </c>
       <c r="AC31" s="3" t="n">
         <v>133058</v>
@@ -4597,7 +4597,7 @@
         <v>5165</v>
       </c>
       <c r="AB32" s="3" t="n">
-        <v>0</v>
+        <v>2601</v>
       </c>
       <c r="AC32" s="3" t="n">
         <v>218319</v>
@@ -4708,16 +4708,16 @@
         <v>0.003865</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA33" s="3" t="n">
         <v>11679</v>
       </c>
       <c r="AB33" s="3" t="n">
-        <v>0</v>
+        <v>1646</v>
       </c>
       <c r="AC33" s="3" t="n">
         <v>170202</v>
@@ -4828,16 +4828,16 @@
         <v>0.003867</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA34" s="3" t="n">
         <v>3417</v>
       </c>
       <c r="AB34" s="3" t="n">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="AC34" s="3" t="n">
         <v>186667</v>
@@ -4957,7 +4957,7 @@
         <v>2538</v>
       </c>
       <c r="AB35" s="3" t="n">
-        <v>0</v>
+        <v>2703</v>
       </c>
       <c r="AC35" s="3" t="n">
         <v>167225</v>
@@ -5077,7 +5077,7 @@
         <v>7852</v>
       </c>
       <c r="AB36" s="3" t="n">
-        <v>2</v>
+        <v>4089</v>
       </c>
       <c r="AC36" s="3" t="n">
         <v>151232</v>
@@ -5188,16 +5188,16 @@
         <v>0.003682</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA37" s="3" t="n">
         <v>2678</v>
       </c>
       <c r="AB37" s="3" t="n">
-        <v>0</v>
+        <v>1135</v>
       </c>
       <c r="AC37" s="3" t="n">
         <v>154363</v>
@@ -5317,7 +5317,7 @@
         <v>2893</v>
       </c>
       <c r="AB38" s="3" t="n">
-        <v>0</v>
+        <v>1704</v>
       </c>
       <c r="AC38" s="3" t="n">
         <v>169197</v>
@@ -5437,7 +5437,7 @@
         <v>3059</v>
       </c>
       <c r="AB39" s="3" t="n">
-        <v>0</v>
+        <v>1465</v>
       </c>
       <c r="AC39" s="3" t="n">
         <v>132271</v>
@@ -5548,7 +5548,7 @@
         <v>0.003755</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>-0</v>
@@ -5557,7 +5557,7 @@
         <v>2060</v>
       </c>
       <c r="AB40" s="3" t="n">
-        <v>0</v>
+        <v>1436</v>
       </c>
       <c r="AC40" s="3" t="n">
         <v>172067</v>
@@ -5677,7 +5677,7 @@
         <v>1989</v>
       </c>
       <c r="AB41" s="3" t="n">
-        <v>0</v>
+        <v>2578</v>
       </c>
       <c r="AC41" s="3" t="n">
         <v>136372</v>
@@ -5797,7 +5797,7 @@
         <v>10878</v>
       </c>
       <c r="AB42" s="3" t="n">
-        <v>3</v>
+        <v>4308</v>
       </c>
       <c r="AC42" s="3" t="n">
         <v>167986</v>
@@ -5917,7 +5917,7 @@
         <v>2064</v>
       </c>
       <c r="AB43" s="3" t="n">
-        <v>0</v>
+        <v>2076</v>
       </c>
       <c r="AC43" s="3" t="n">
         <v>167127</v>
@@ -6037,7 +6037,7 @@
         <v>1117</v>
       </c>
       <c r="AB44" s="3" t="n">
-        <v>0</v>
+        <v>1214</v>
       </c>
       <c r="AC44" s="3" t="n">
         <v>113148</v>
@@ -6148,16 +6148,16 @@
         <v>0.003683</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA45" s="3" t="n">
         <v>2526</v>
       </c>
       <c r="AB45" s="3" t="n">
-        <v>0</v>
+        <v>3903</v>
       </c>
       <c r="AC45" s="3" t="n">
         <v>238412</v>
@@ -6277,7 +6277,7 @@
         <v>5600</v>
       </c>
       <c r="AB46" s="3" t="n">
-        <v>0</v>
+        <v>4264</v>
       </c>
       <c r="AC46" s="3" t="n">
         <v>93342</v>
@@ -6391,13 +6391,13 @@
         <v>-0</v>
       </c>
       <c r="Z47" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA47" s="3" t="n">
         <v>2752</v>
       </c>
       <c r="AB47" s="3" t="n">
-        <v>0</v>
+        <v>1378</v>
       </c>
       <c r="AC47" s="3" t="n">
         <v>150423</v>
@@ -6517,7 +6517,7 @@
         <v>3379</v>
       </c>
       <c r="AB48" s="3" t="n">
-        <v>0</v>
+        <v>1949</v>
       </c>
       <c r="AC48" s="3" t="n">
         <v>198424</v>
@@ -6637,7 +6637,7 @@
         <v>7680</v>
       </c>
       <c r="AB49" s="3" t="n">
-        <v>0</v>
+        <v>1816</v>
       </c>
       <c r="AC49" s="3" t="n">
         <v>107335</v>
@@ -6748,16 +6748,16 @@
         <v>0.00308</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z50" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA50" s="3" t="n">
         <v>1472</v>
       </c>
       <c r="AB50" s="3" t="n">
-        <v>0</v>
+        <v>897</v>
       </c>
       <c r="AC50" s="3" t="n">
         <v>126408</v>
@@ -6877,7 +6877,7 @@
         <v>2152</v>
       </c>
       <c r="AB51" s="3" t="n">
-        <v>0</v>
+        <v>2187</v>
       </c>
       <c r="AC51" s="3" t="n">
         <v>204631</v>
@@ -6997,7 +6997,7 @@
         <v>2303</v>
       </c>
       <c r="AB52" s="3" t="n">
-        <v>0</v>
+        <v>2241</v>
       </c>
       <c r="AC52" s="3" t="n">
         <v>236874</v>
@@ -7117,7 +7117,7 @@
         <v>930</v>
       </c>
       <c r="AB53" s="3" t="n">
-        <v>0</v>
+        <v>1093</v>
       </c>
       <c r="AC53" s="3" t="n">
         <v>134090</v>
@@ -7237,7 +7237,7 @@
         <v>5461</v>
       </c>
       <c r="AB54" s="3" t="n">
-        <v>2</v>
+        <v>2706</v>
       </c>
       <c r="AC54" s="3" t="n">
         <v>113002</v>
@@ -7357,7 +7357,7 @@
         <v>1293</v>
       </c>
       <c r="AB55" s="3" t="n">
-        <v>0</v>
+        <v>1252</v>
       </c>
       <c r="AC55" s="3" t="n">
         <v>128863</v>
@@ -7477,7 +7477,7 @@
         <v>4129</v>
       </c>
       <c r="AB56" s="3" t="n">
-        <v>0</v>
+        <v>1292</v>
       </c>
       <c r="AC56" s="3" t="n">
         <v>194254</v>
@@ -7597,7 +7597,7 @@
         <v>2734</v>
       </c>
       <c r="AB57" s="3" t="n">
-        <v>0</v>
+        <v>1935</v>
       </c>
       <c r="AC57" s="3" t="n">
         <v>185793</v>
@@ -7717,7 +7717,7 @@
         <v>2101</v>
       </c>
       <c r="AB58" s="3" t="n">
-        <v>0</v>
+        <v>1670</v>
       </c>
       <c r="AC58" s="3" t="n">
         <v>138620</v>
@@ -7828,16 +7828,16 @@
         <v>0.002932</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="3" t="n">
         <v>2443</v>
       </c>
       <c r="AB59" s="3" t="n">
-        <v>0</v>
+        <v>2283</v>
       </c>
       <c r="AC59" s="3" t="n">
         <v>201013</v>
@@ -7957,7 +7957,7 @@
         <v>2122</v>
       </c>
       <c r="AB60" s="3" t="n">
-        <v>0</v>
+        <v>2648</v>
       </c>
       <c r="AC60" s="3" t="n">
         <v>156360</v>
@@ -8077,7 +8077,7 @@
         <v>11662</v>
       </c>
       <c r="AB61" s="3" t="n">
-        <v>0</v>
+        <v>3951</v>
       </c>
       <c r="AC61" s="3" t="n">
         <v>145072</v>
@@ -8188,7 +8188,7 @@
         <v>0.003378</v>
       </c>
       <c r="Y62" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="3" t="n">
         <v>0</v>
@@ -8197,7 +8197,7 @@
         <v>2142</v>
       </c>
       <c r="AB62" s="3" t="n">
-        <v>0</v>
+        <v>1094</v>
       </c>
       <c r="AC62" s="3" t="n">
         <v>133690</v>
@@ -8308,16 +8308,16 @@
         <v>0.003147</v>
       </c>
       <c r="Y63" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z63" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA63" s="3" t="n">
         <v>3557</v>
       </c>
       <c r="AB63" s="3" t="n">
-        <v>0</v>
+        <v>1502</v>
       </c>
       <c r="AC63" s="3" t="n">
         <v>134853</v>
@@ -8437,7 +8437,7 @@
         <v>3344</v>
       </c>
       <c r="AB64" s="3" t="n">
-        <v>0</v>
+        <v>1851</v>
       </c>
       <c r="AC64" s="3" t="n">
         <v>138200</v>
@@ -8557,7 +8557,7 @@
         <v>4171</v>
       </c>
       <c r="AB65" s="3" t="n">
-        <v>0</v>
+        <v>2128</v>
       </c>
       <c r="AC65" s="3" t="n">
         <v>105697</v>
@@ -8668,7 +8668,7 @@
         <v>0.00324</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z66" s="3" t="n">
         <v>-0</v>
@@ -8677,7 +8677,7 @@
         <v>2524</v>
       </c>
       <c r="AB66" s="3" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="AC66" s="3" t="n">
         <v>143663</v>
@@ -8797,7 +8797,7 @@
         <v>3819</v>
       </c>
       <c r="AB67" s="3" t="n">
-        <v>0</v>
+        <v>486</v>
       </c>
       <c r="AC67" s="3" t="n">
         <v>78578</v>
@@ -8911,13 +8911,13 @@
         <v>-0</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA68" s="3" t="n">
         <v>1130</v>
       </c>
       <c r="AB68" s="3" t="n">
-        <v>0</v>
+        <v>1585</v>
       </c>
       <c r="AC68" s="3" t="n">
         <v>104492</v>
@@ -9037,7 +9037,7 @@
         <v>3171</v>
       </c>
       <c r="AB69" s="3" t="n">
-        <v>0</v>
+        <v>2624</v>
       </c>
       <c r="AC69" s="3" t="n">
         <v>198885</v>
@@ -9157,7 +9157,7 @@
         <v>9844</v>
       </c>
       <c r="AB70" s="3" t="n">
-        <v>6</v>
+        <v>3710</v>
       </c>
       <c r="AC70" s="3" t="n">
         <v>160814</v>
@@ -9277,7 +9277,7 @@
         <v>5618</v>
       </c>
       <c r="AB71" s="3" t="n">
-        <v>0</v>
+        <v>671</v>
       </c>
       <c r="AC71" s="3" t="n">
         <v>107984</v>
@@ -9397,7 +9397,7 @@
         <v>1701</v>
       </c>
       <c r="AB72" s="3" t="n">
-        <v>0</v>
+        <v>1694</v>
       </c>
       <c r="AC72" s="3" t="n">
         <v>179203</v>
@@ -9508,16 +9508,16 @@
         <v>0.003381</v>
       </c>
       <c r="Y73" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA73" s="3" t="n">
         <v>1306</v>
       </c>
       <c r="AB73" s="3" t="n">
-        <v>0</v>
+        <v>1738</v>
       </c>
       <c r="AC73" s="3" t="n">
         <v>175579</v>
@@ -9637,7 +9637,7 @@
         <v>1868</v>
       </c>
       <c r="AB74" s="3" t="n">
-        <v>0</v>
+        <v>1859</v>
       </c>
       <c r="AC74" s="3" t="n">
         <v>124289</v>
@@ -9757,7 +9757,7 @@
         <v>2678</v>
       </c>
       <c r="AB75" s="3" t="n">
-        <v>0</v>
+        <v>2266</v>
       </c>
       <c r="AC75" s="3" t="n">
         <v>140016</v>
@@ -9877,7 +9877,7 @@
         <v>548</v>
       </c>
       <c r="AB76" s="3" t="n">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="AC76" s="3" t="n">
         <v>90630</v>
@@ -9997,7 +9997,7 @@
         <v>3194</v>
       </c>
       <c r="AB77" s="3" t="n">
-        <v>0</v>
+        <v>2985</v>
       </c>
       <c r="AC77" s="3" t="n">
         <v>149832</v>
@@ -10117,7 +10117,7 @@
         <v>11227</v>
       </c>
       <c r="AB78" s="3" t="n">
-        <v>0</v>
+        <v>4580</v>
       </c>
       <c r="AC78" s="3" t="n">
         <v>113929</v>
@@ -10237,7 +10237,7 @@
         <v>2463</v>
       </c>
       <c r="AB79" s="3" t="n">
-        <v>0</v>
+        <v>1263</v>
       </c>
       <c r="AC79" s="3" t="n">
         <v>115651</v>
@@ -10357,7 +10357,7 @@
         <v>2602</v>
       </c>
       <c r="AB80" s="3" t="n">
-        <v>0</v>
+        <v>2392</v>
       </c>
       <c r="AC80" s="3" t="n">
         <v>173030</v>
@@ -10477,7 +10477,7 @@
         <v>7421</v>
       </c>
       <c r="AB81" s="3" t="n">
-        <v>0</v>
+        <v>2798</v>
       </c>
       <c r="AC81" s="3" t="n">
         <v>113041</v>
@@ -10591,13 +10591,13 @@
         <v>0</v>
       </c>
       <c r="Z82" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA82" s="3" t="n">
         <v>3690</v>
       </c>
       <c r="AB82" s="3" t="n">
-        <v>0</v>
+        <v>1638</v>
       </c>
       <c r="AC82" s="3" t="n">
         <v>150752</v>
@@ -10717,7 +10717,7 @@
         <v>1694</v>
       </c>
       <c r="AB83" s="3" t="n">
-        <v>0</v>
+        <v>2091</v>
       </c>
       <c r="AC83" s="3" t="n">
         <v>133621</v>
@@ -10837,7 +10837,7 @@
         <v>1745</v>
       </c>
       <c r="AB84" s="3" t="n">
-        <v>0</v>
+        <v>710</v>
       </c>
       <c r="AC84" s="3" t="n">
         <v>114450</v>
@@ -10951,13 +10951,13 @@
         <v>0</v>
       </c>
       <c r="Z85" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA85" s="3" t="n">
         <v>765</v>
       </c>
       <c r="AB85" s="3" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="AC85" s="3" t="n">
         <v>122290</v>
@@ -11077,7 +11077,7 @@
         <v>871</v>
       </c>
       <c r="AB86" s="3" t="n">
-        <v>0</v>
+        <v>1073</v>
       </c>
       <c r="AC86" s="3" t="n">
         <v>134524</v>
@@ -11197,7 +11197,7 @@
         <v>1472</v>
       </c>
       <c r="AB87" s="3" t="n">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="AC87" s="3" t="n">
         <v>103066</v>
@@ -11317,7 +11317,7 @@
         <v>1537</v>
       </c>
       <c r="AB88" s="3" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC88" s="3" t="n">
         <v>101231</v>
@@ -11437,7 +11437,7 @@
         <v>2935</v>
       </c>
       <c r="AB89" s="3" t="n">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="AC89" s="3" t="n">
         <v>86794</v>
@@ -11557,7 +11557,7 @@
         <v>1414</v>
       </c>
       <c r="AB90" s="3" t="n">
-        <v>0</v>
+        <v>842</v>
       </c>
       <c r="AC90" s="3" t="n">
         <v>81733</v>
@@ -11668,16 +11668,16 @@
         <v>0.002422</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA91" s="3" t="n">
         <v>3818</v>
       </c>
       <c r="AB91" s="3" t="n">
-        <v>0</v>
+        <v>2938</v>
       </c>
       <c r="AC91" s="3" t="n">
         <v>199738</v>
@@ -11788,16 +11788,16 @@
         <v>0.002739</v>
       </c>
       <c r="Y92" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z92" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA92" s="3" t="n">
         <v>2843</v>
       </c>
       <c r="AB92" s="3" t="n">
-        <v>0</v>
+        <v>1286</v>
       </c>
       <c r="AC92" s="3" t="n">
         <v>94308</v>
@@ -11917,7 +11917,7 @@
         <v>12443</v>
       </c>
       <c r="AB93" s="3" t="n">
-        <v>11</v>
+        <v>3476</v>
       </c>
       <c r="AC93" s="3" t="n">
         <v>134228</v>
@@ -12028,16 +12028,16 @@
         <v>0.003001</v>
       </c>
       <c r="Y94" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="n">
         <v>3835</v>
       </c>
       <c r="AB94" s="3" t="n">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="AC94" s="3" t="n">
         <v>108098</v>
@@ -12157,7 +12157,7 @@
         <v>5482</v>
       </c>
       <c r="AB95" s="3" t="n">
-        <v>0</v>
+        <v>2095</v>
       </c>
       <c r="AC95" s="3" t="n">
         <v>130239</v>
@@ -12268,16 +12268,16 @@
         <v>0.002802</v>
       </c>
       <c r="Y96" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z96" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA96" s="3" t="n">
         <v>2203</v>
       </c>
       <c r="AB96" s="3" t="n">
-        <v>0</v>
+        <v>941</v>
       </c>
       <c r="AC96" s="3" t="n">
         <v>101511</v>
@@ -12397,7 +12397,7 @@
         <v>1517</v>
       </c>
       <c r="AB97" s="3" t="n">
-        <v>0</v>
+        <v>846</v>
       </c>
       <c r="AC97" s="3" t="n">
         <v>112891</v>
@@ -12508,16 +12508,16 @@
         <v>0.002646</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>4116</v>
       </c>
       <c r="AB98" s="3" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="AC98" s="3" t="n">
         <v>119264</v>
@@ -12637,7 +12637,7 @@
         <v>671</v>
       </c>
       <c r="AB99" s="3" t="n">
-        <v>0</v>
+        <v>544</v>
       </c>
       <c r="AC99" s="3" t="n">
         <v>81048</v>
@@ -12757,7 +12757,7 @@
         <v>8108</v>
       </c>
       <c r="AB100" s="3" t="n">
-        <v>0</v>
+        <v>3997</v>
       </c>
       <c r="AC100" s="3" t="n">
         <v>98352</v>
@@ -12877,7 +12877,7 @@
         <v>969</v>
       </c>
       <c r="AB101" s="3" t="n">
-        <v>0</v>
+        <v>1423</v>
       </c>
       <c r="AC101" s="3" t="n">
         <v>130625</v>
@@ -12991,13 +12991,13 @@
         <v>-0</v>
       </c>
       <c r="Z102" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="n">
         <v>1151</v>
       </c>
       <c r="AB102" s="3" t="n">
-        <v>0</v>
+        <v>1035</v>
       </c>
       <c r="AC102" s="3" t="n">
         <v>70779</v>
@@ -13117,7 +13117,7 @@
         <v>1724</v>
       </c>
       <c r="AB103" s="3" t="n">
-        <v>0</v>
+        <v>1146</v>
       </c>
       <c r="AC103" s="3" t="n">
         <v>125917</v>
@@ -13237,7 +13237,7 @@
         <v>1943</v>
       </c>
       <c r="AB104" s="3" t="n">
-        <v>0</v>
+        <v>1094</v>
       </c>
       <c r="AC104" s="3" t="n">
         <v>98098</v>
@@ -13357,7 +13357,7 @@
         <v>1123</v>
       </c>
       <c r="AB105" s="3" t="n">
-        <v>0</v>
+        <v>4072</v>
       </c>
       <c r="AC105" s="3" t="n">
         <v>121897</v>
@@ -13477,7 +13477,7 @@
         <v>3061</v>
       </c>
       <c r="AB106" s="3" t="n">
-        <v>0</v>
+        <v>3431</v>
       </c>
       <c r="AC106" s="3" t="n">
         <v>95398</v>
@@ -13597,7 +13597,7 @@
         <v>1288</v>
       </c>
       <c r="AB107" s="3" t="n">
-        <v>0</v>
+        <v>454</v>
       </c>
       <c r="AC107" s="3" t="n">
         <v>70204</v>
@@ -13708,16 +13708,16 @@
         <v>0.00271</v>
       </c>
       <c r="Y108" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z108" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA108" s="3" t="n">
         <v>2304</v>
       </c>
       <c r="AB108" s="3" t="n">
-        <v>0</v>
+        <v>2524</v>
       </c>
       <c r="AC108" s="3" t="n">
         <v>98857</v>
@@ -13837,7 +13837,7 @@
         <v>2711</v>
       </c>
       <c r="AB109" s="3" t="n">
-        <v>0</v>
+        <v>1760</v>
       </c>
       <c r="AC109" s="3" t="n">
         <v>99164</v>
@@ -13957,7 +13957,7 @@
         <v>5645</v>
       </c>
       <c r="AB110" s="3" t="n">
-        <v>0</v>
+        <v>1174</v>
       </c>
       <c r="AC110" s="3" t="n">
         <v>81009</v>
@@ -14077,7 +14077,7 @@
         <v>5293</v>
       </c>
       <c r="AB111" s="3" t="n">
-        <v>0</v>
+        <v>1799</v>
       </c>
       <c r="AC111" s="3" t="n">
         <v>82617</v>
@@ -14197,7 +14197,7 @@
         <v>1092</v>
       </c>
       <c r="AB112" s="3" t="n">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="AC112" s="3" t="n">
         <v>70552</v>
@@ -14308,16 +14308,16 @@
         <v>0.002608</v>
       </c>
       <c r="Y113" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z113" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA113" s="3" t="n">
         <v>3508</v>
       </c>
       <c r="AB113" s="3" t="n">
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="AC113" s="3" t="n">
         <v>116851</v>
@@ -14427,7 +14427,7 @@
         <v>1871</v>
       </c>
       <c r="AB114" s="3" t="n">
-        <v>0</v>
+        <v>1654</v>
       </c>
       <c r="AC114" s="3" t="n">
         <v>102080</v>
@@ -14528,16 +14528,16 @@
         <v>0.003037</v>
       </c>
       <c r="Y115" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z115" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA115" s="3" t="n">
         <v>2287</v>
       </c>
       <c r="AB115" s="3" t="n">
-        <v>0</v>
+        <v>1744</v>
       </c>
       <c r="AC115" s="3" t="n">
         <v>69784</v>
@@ -14638,16 +14638,16 @@
         <v>0.002434</v>
       </c>
       <c r="Y116" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA116" s="3" t="n">
         <v>1796</v>
       </c>
       <c r="AB116" s="3" t="n">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="AC116" s="3" t="n">
         <v>96559</v>
@@ -14757,7 +14757,7 @@
         <v>2127</v>
       </c>
       <c r="AB117" s="3" t="n">
-        <v>0</v>
+        <v>2482</v>
       </c>
       <c r="AC117" s="3" t="n">
         <v>94208</v>
@@ -14858,16 +14858,16 @@
         <v>0.002517</v>
       </c>
       <c r="Y118" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA118" s="3" t="n">
         <v>4137</v>
       </c>
       <c r="AB118" s="3" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="AC118" s="3" t="n">
         <v>106284</v>
@@ -14977,7 +14977,7 @@
         <v>2453</v>
       </c>
       <c r="AB119" s="3" t="n">
-        <v>0</v>
+        <v>2124</v>
       </c>
       <c r="AC119" s="3" t="n">
         <v>127606</v>
@@ -15087,7 +15087,7 @@
         <v>3031</v>
       </c>
       <c r="AB120" s="3" t="n">
-        <v>0</v>
+        <v>4360</v>
       </c>
       <c r="AC120" s="3" t="n">
         <v>99946</v>
@@ -15197,7 +15197,7 @@
         <v>2616</v>
       </c>
       <c r="AB121" s="3" t="n">
-        <v>0</v>
+        <v>1106</v>
       </c>
       <c r="AC121" s="3" t="n">
         <v>107078</v>
@@ -15301,13 +15301,13 @@
         <v>0</v>
       </c>
       <c r="Z122" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA122" s="3" t="n">
         <v>4089</v>
       </c>
       <c r="AB122" s="3" t="n">
-        <v>0</v>
+        <v>841</v>
       </c>
       <c r="AC122" s="3" t="n">
         <v>88872</v>
@@ -15417,7 +15417,7 @@
         <v>1575</v>
       </c>
       <c r="AB123" s="3" t="n">
-        <v>0</v>
+        <v>543</v>
       </c>
       <c r="AC123" s="3" t="n">
         <v>83461</v>
@@ -15527,7 +15527,7 @@
         <v>2044</v>
       </c>
       <c r="AB124" s="3" t="n">
-        <v>0</v>
+        <v>1678</v>
       </c>
       <c r="AC124" s="3" t="n">
         <v>136782</v>
@@ -15637,7 +15637,7 @@
         <v>5438</v>
       </c>
       <c r="AB125" s="3" t="n">
-        <v>9</v>
+        <v>2742</v>
       </c>
       <c r="AC125" s="3" t="n">
         <v>122915</v>
@@ -15747,7 +15747,7 @@
         <v>2532</v>
       </c>
       <c r="AB126" s="3" t="n">
-        <v>0</v>
+        <v>936</v>
       </c>
       <c r="AC126" s="3" t="n">
         <v>102505</v>
@@ -15857,7 +15857,7 @@
         <v>1776</v>
       </c>
       <c r="AB127" s="3" t="n">
-        <v>0</v>
+        <v>1041</v>
       </c>
       <c r="AC127" s="3" t="n">
         <v>87338</v>
@@ -15967,7 +15967,7 @@
         <v>2163</v>
       </c>
       <c r="AB128" s="3" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="AC128" s="3" t="n">
         <v>48581</v>
@@ -16077,7 +16077,7 @@
         <v>2260</v>
       </c>
       <c r="AB129" s="3" t="n">
-        <v>0</v>
+        <v>517</v>
       </c>
       <c r="AC129" s="3" t="n">
         <v>74485</v>
@@ -16187,7 +16187,7 @@
         <v>2601</v>
       </c>
       <c r="AB130" s="3" t="n">
-        <v>0</v>
+        <v>726</v>
       </c>
       <c r="AC130" s="3" t="n">
         <v>67472</v>
@@ -16297,7 +16297,7 @@
         <v>3092</v>
       </c>
       <c r="AB131" s="3" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="AC131" s="3" t="n">
         <v>71122</v>
@@ -16407,7 +16407,7 @@
         <v>3242</v>
       </c>
       <c r="AB132" s="3" t="n">
-        <v>0</v>
+        <v>2055</v>
       </c>
       <c r="AC132" s="3" t="n">
         <v>54219</v>
@@ -16517,7 +16517,7 @@
         <v>3944</v>
       </c>
       <c r="AB133" s="3" t="n">
-        <v>0</v>
+        <v>2409</v>
       </c>
       <c r="AC133" s="3" t="n">
         <v>49283</v>
@@ -16621,13 +16621,13 @@
         <v>0</v>
       </c>
       <c r="Z134" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA134" s="3" t="n">
         <v>5101</v>
       </c>
       <c r="AB134" s="3" t="n">
-        <v>0</v>
+        <v>1026</v>
       </c>
       <c r="AC134" s="3" t="n">
         <v>62638</v>
@@ -16737,7 +16737,7 @@
         <v>7893</v>
       </c>
       <c r="AB135" s="3" t="n">
-        <v>22</v>
+        <v>4712</v>
       </c>
       <c r="AC135" s="3" t="n">
         <v>115211</v>
@@ -16847,7 +16847,7 @@
         <v>1080</v>
       </c>
       <c r="AB136" s="3" t="n">
-        <v>0</v>
+        <v>1457</v>
       </c>
       <c r="AC136" s="3" t="n">
         <v>82227</v>
@@ -16957,7 +16957,7 @@
         <v>1419</v>
       </c>
       <c r="AB137" s="3" t="n">
-        <v>0</v>
+        <v>1794</v>
       </c>
       <c r="AC137" s="3" t="n">
         <v>66996</v>
@@ -17058,7 +17058,7 @@
         <v>0.002271</v>
       </c>
       <c r="Y138" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z138" s="3" t="n">
         <v>0</v>
@@ -17067,7 +17067,7 @@
         <v>5041</v>
       </c>
       <c r="AB138" s="3" t="n">
-        <v>0</v>
+        <v>1673</v>
       </c>
       <c r="AC138" s="3" t="n">
         <v>111209</v>
@@ -17168,16 +17168,16 @@
         <v>0.002766</v>
       </c>
       <c r="Y139" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z139" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA139" s="3" t="n">
         <v>1737</v>
       </c>
       <c r="AB139" s="3" t="n">
-        <v>0</v>
+        <v>484</v>
       </c>
       <c r="AC139" s="3" t="n">
         <v>63576</v>
@@ -17287,7 +17287,7 @@
         <v>980</v>
       </c>
       <c r="AB140" s="3" t="n">
-        <v>0</v>
+        <v>844</v>
       </c>
       <c r="AC140" s="3" t="n">
         <v>106840</v>
@@ -17397,7 +17397,7 @@
         <v>3546</v>
       </c>
       <c r="AB141" s="3" t="n">
-        <v>0</v>
+        <v>1978</v>
       </c>
       <c r="AC141" s="3" t="n">
         <v>136770</v>
@@ -17507,7 +17507,7 @@
         <v>828</v>
       </c>
       <c r="AB142" s="3" t="n">
-        <v>0</v>
+        <v>959</v>
       </c>
       <c r="AC142" s="3" t="n">
         <v>67674</v>
@@ -17617,7 +17617,7 @@
         <v>4555</v>
       </c>
       <c r="AB143" s="3" t="n">
-        <v>0</v>
+        <v>3296</v>
       </c>
       <c r="AC143" s="3" t="n">
         <v>81994</v>
@@ -17727,7 +17727,7 @@
         <v>1027</v>
       </c>
       <c r="AB144" s="3" t="n">
-        <v>0</v>
+        <v>1803</v>
       </c>
       <c r="AC144" s="3" t="n">
         <v>58587</v>
@@ -17837,7 +17837,7 @@
         <v>2832</v>
       </c>
       <c r="AB145" s="3" t="n">
-        <v>0</v>
+        <v>4744</v>
       </c>
       <c r="AC145" s="3" t="n">
         <v>102793</v>
@@ -17947,7 +17947,7 @@
         <v>2904</v>
       </c>
       <c r="AB146" s="3" t="n">
-        <v>0</v>
+        <v>1084</v>
       </c>
       <c r="AC146" s="3" t="n">
         <v>122200</v>
@@ -18057,7 +18057,7 @@
         <v>6956</v>
       </c>
       <c r="AB147" s="3" t="n">
-        <v>0</v>
+        <v>6744</v>
       </c>
       <c r="AC147" s="3" t="n">
         <v>111381</v>
@@ -18167,7 +18167,7 @@
         <v>704</v>
       </c>
       <c r="AB148" s="3" t="n">
-        <v>0</v>
+        <v>1924</v>
       </c>
       <c r="AC148" s="3" t="n">
         <v>116928</v>
@@ -18268,16 +18268,16 @@
         <v>0.002226</v>
       </c>
       <c r="Y149" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z149" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA149" s="3" t="n">
         <v>2856</v>
       </c>
       <c r="AB149" s="3" t="n">
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="AC149" s="3" t="n">
         <v>93034</v>
@@ -18387,7 +18387,7 @@
         <v>8054</v>
       </c>
       <c r="AB150" s="3" t="n">
-        <v>10</v>
+        <v>2646</v>
       </c>
       <c r="AC150" s="3" t="n">
         <v>94693</v>
@@ -18488,16 +18488,16 @@
         <v>0.002324</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>1662</v>
       </c>
       <c r="AB151" s="3" t="n">
-        <v>0</v>
+        <v>959</v>
       </c>
       <c r="AC151" s="3" t="n">
         <v>93168</v>
@@ -18607,7 +18607,7 @@
         <v>2838</v>
       </c>
       <c r="AB152" s="3" t="n">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="AC152" s="3" t="n">
         <v>70575</v>
@@ -18711,13 +18711,13 @@
         <v>0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>2916</v>
       </c>
       <c r="AB153" s="3" t="n">
-        <v>0</v>
+        <v>1196</v>
       </c>
       <c r="AC153" s="3" t="n">
         <v>81086</v>
@@ -18827,7 +18827,7 @@
         <v>3166</v>
       </c>
       <c r="AB154" s="3" t="n">
-        <v>0</v>
+        <v>2741</v>
       </c>
       <c r="AC154" s="3" t="n">
         <v>140340</v>
@@ -18937,7 +18937,7 @@
         <v>1121</v>
       </c>
       <c r="AB155" s="3" t="n">
-        <v>0</v>
+        <v>1316</v>
       </c>
       <c r="AC155" s="3" t="n">
         <v>91863</v>
@@ -19041,13 +19041,13 @@
         <v>-0</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA156" s="3" t="n">
         <v>1967</v>
       </c>
       <c r="AB156" s="3" t="n">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="AC156" s="3" t="n">
         <v>92961</v>
@@ -19157,7 +19157,7 @@
         <v>5494</v>
       </c>
       <c r="AB157" s="3" t="n">
-        <v>0</v>
+        <v>5766</v>
       </c>
       <c r="AC157" s="3" t="n">
         <v>100593</v>
@@ -19267,7 +19267,7 @@
         <v>609</v>
       </c>
       <c r="AB158" s="3" t="n">
-        <v>0</v>
+        <v>2369</v>
       </c>
       <c r="AC158" s="3" t="n">
         <v>49759</v>
@@ -19377,7 +19377,7 @@
         <v>6112</v>
       </c>
       <c r="AB159" s="3" t="n">
-        <v>2</v>
+        <v>3276</v>
       </c>
       <c r="AC159" s="3" t="n">
         <v>129180</v>
@@ -19478,16 +19478,16 @@
         <v>0.001886</v>
       </c>
       <c r="Y160" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA160" s="3" t="n">
         <v>1626</v>
       </c>
       <c r="AB160" s="3" t="n">
-        <v>0</v>
+        <v>1238</v>
       </c>
       <c r="AC160" s="3" t="n">
         <v>126695</v>
@@ -19597,7 +19597,7 @@
         <v>796</v>
       </c>
       <c r="AB161" s="3" t="n">
-        <v>0</v>
+        <v>712</v>
       </c>
       <c r="AC161" s="3" t="n">
         <v>74518</v>
@@ -19698,7 +19698,7 @@
         <v>0.002359</v>
       </c>
       <c r="Y162" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z162" s="3" t="n">
         <v>0</v>
@@ -19707,7 +19707,7 @@
         <v>1949</v>
       </c>
       <c r="AB162" s="3" t="n">
-        <v>0</v>
+        <v>705</v>
       </c>
       <c r="AC162" s="3" t="n">
         <v>83749</v>
@@ -19808,16 +19808,16 @@
         <v>0.002078</v>
       </c>
       <c r="Y163" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA163" s="3" t="n">
         <v>1844</v>
       </c>
       <c r="AB163" s="3" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="AC163" s="3" t="n">
         <v>79850</v>
@@ -19927,7 +19927,7 @@
         <v>5986</v>
       </c>
       <c r="AB164" s="3" t="n">
-        <v>0</v>
+        <v>3523</v>
       </c>
       <c r="AC164" s="3" t="n">
         <v>89170</v>
@@ -20037,7 +20037,7 @@
         <v>1727</v>
       </c>
       <c r="AB165" s="3" t="n">
-        <v>0</v>
+        <v>3090</v>
       </c>
       <c r="AC165" s="3" t="n">
         <v>134213</v>
@@ -20147,7 +20147,7 @@
         <v>2464</v>
       </c>
       <c r="AB166" s="3" t="n">
-        <v>0</v>
+        <v>635</v>
       </c>
       <c r="AC166" s="3" t="n">
         <v>64011</v>
@@ -20257,7 +20257,7 @@
         <v>284</v>
       </c>
       <c r="AB167" s="3" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="AC167" s="3" t="n">
         <v>72696</v>
@@ -20367,7 +20367,7 @@
         <v>1141</v>
       </c>
       <c r="AB168" s="3" t="n">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="AC168" s="3" t="n">
         <v>74109</v>
@@ -20477,7 +20477,7 @@
         <v>1147</v>
       </c>
       <c r="AB169" s="3" t="n">
-        <v>0</v>
+        <v>905</v>
       </c>
       <c r="AC169" s="3" t="n">
         <v>62895</v>
@@ -20578,16 +20578,16 @@
         <v>0.002054</v>
       </c>
       <c r="Y170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA170" s="3" t="n">
         <v>1712</v>
       </c>
       <c r="AB170" s="3" t="n">
-        <v>0</v>
+        <v>1635</v>
       </c>
       <c r="AC170" s="3" t="n">
         <v>134858</v>
@@ -20697,7 +20697,7 @@
         <v>2411</v>
       </c>
       <c r="AB171" s="3" t="n">
-        <v>0</v>
+        <v>1196</v>
       </c>
       <c r="AC171" s="3" t="n">
         <v>50587</v>
@@ -20798,16 +20798,16 @@
         <v>0.002328</v>
       </c>
       <c r="Y172" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA172" s="3" t="n">
         <v>1267</v>
       </c>
       <c r="AB172" s="3" t="n">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="AC172" s="3" t="n">
         <v>45598</v>
@@ -20917,7 +20917,7 @@
         <v>1316</v>
       </c>
       <c r="AB173" s="3" t="n">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="AC173" s="3" t="n">
         <v>108026</v>
@@ -21027,7 +21027,7 @@
         <v>7221</v>
       </c>
       <c r="AB174" s="3" t="n">
-        <v>0</v>
+        <v>2655</v>
       </c>
       <c r="AC174" s="3" t="n">
         <v>92508</v>
@@ -21128,16 +21128,16 @@
         <v>0.002174</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA175" s="3" t="n">
         <v>1957</v>
       </c>
       <c r="AB175" s="3" t="n">
-        <v>0</v>
+        <v>1783</v>
       </c>
       <c r="AC175" s="3" t="n">
         <v>118978</v>
@@ -21247,7 +21247,7 @@
         <v>1209</v>
       </c>
       <c r="AB176" s="3" t="n">
-        <v>0</v>
+        <v>827</v>
       </c>
       <c r="AC176" s="3" t="n">
         <v>84737</v>
@@ -21348,16 +21348,16 @@
         <v>0.002421</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>857</v>
       </c>
       <c r="AB177" s="3" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="AC177" s="3" t="n">
         <v>62421</v>
@@ -21467,7 +21467,7 @@
         <v>1559</v>
       </c>
       <c r="AB178" s="3" t="n">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="AC178" s="3" t="n">
         <v>60461</v>
@@ -21577,7 +21577,7 @@
         <v>5398</v>
       </c>
       <c r="AB179" s="3" t="n">
-        <v>0</v>
+        <v>5575</v>
       </c>
       <c r="AC179" s="3" t="n">
         <v>103555</v>
@@ -21687,7 +21687,7 @@
         <v>691</v>
       </c>
       <c r="AB180" s="3" t="n">
-        <v>0</v>
+        <v>787</v>
       </c>
       <c r="AC180" s="3" t="n">
         <v>101204</v>
@@ -21797,7 +21797,7 @@
         <v>3769</v>
       </c>
       <c r="AB181" s="3" t="n">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="AC181" s="3" t="n">
         <v>55280</v>
@@ -21907,7 +21907,7 @@
         <v>1727</v>
       </c>
       <c r="AB182" s="3" t="n">
-        <v>0</v>
+        <v>977</v>
       </c>
       <c r="AC182" s="3" t="n">
         <v>78300</v>
@@ -22008,7 +22008,7 @@
         <v>0.002155</v>
       </c>
       <c r="Y183" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z183" s="3" t="n">
         <v>-0</v>
@@ -22017,7 +22017,7 @@
         <v>1407</v>
       </c>
       <c r="AB183" s="3" t="n">
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="AC183" s="3" t="n">
         <v>96872</v>
@@ -22127,7 +22127,7 @@
         <v>1085</v>
       </c>
       <c r="AB184" s="3" t="n">
-        <v>0</v>
+        <v>2976</v>
       </c>
       <c r="AC184" s="3" t="n">
         <v>74782</v>
@@ -22231,13 +22231,13 @@
         <v>0</v>
       </c>
       <c r="Z185" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA185" s="3" t="n">
         <v>1124</v>
       </c>
       <c r="AB185" s="3" t="n">
-        <v>0</v>
+        <v>2118</v>
       </c>
       <c r="AC185" s="3" t="n">
         <v>136683</v>
@@ -22347,7 +22347,7 @@
         <v>1315</v>
       </c>
       <c r="AB186" s="3" t="n">
-        <v>0</v>
+        <v>1526</v>
       </c>
       <c r="AC186" s="3" t="n">
         <v>75683</v>
@@ -22457,7 +22457,7 @@
         <v>1395</v>
       </c>
       <c r="AB187" s="3" t="n">
-        <v>0</v>
+        <v>1873</v>
       </c>
       <c r="AC187" s="3" t="n">
         <v>90787</v>
@@ -22567,7 +22567,7 @@
         <v>902</v>
       </c>
       <c r="AB188" s="3" t="n">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="AC188" s="3" t="n">
         <v>100854</v>
@@ -22668,16 +22668,16 @@
         <v>0.002267</v>
       </c>
       <c r="Y189" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z189" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA189" s="3" t="n">
         <v>1846</v>
       </c>
       <c r="AB189" s="3" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="AC189" s="3" t="n">
         <v>47371</v>
@@ -22787,7 +22787,7 @@
         <v>987</v>
       </c>
       <c r="AB190" s="3" t="n">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="AC190" s="3" t="n">
         <v>87150</v>
@@ -22897,7 +22897,7 @@
         <v>1858</v>
       </c>
       <c r="AB191" s="3" t="n">
-        <v>0</v>
+        <v>1022</v>
       </c>
       <c r="AC191" s="3" t="n">
         <v>91821</v>
@@ -23007,7 +23007,7 @@
         <v>963</v>
       </c>
       <c r="AB192" s="3" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="AC192" s="3" t="n">
         <v>60331</v>
@@ -23117,7 +23117,7 @@
         <v>1460</v>
       </c>
       <c r="AB193" s="3" t="n">
-        <v>0</v>
+        <v>1734</v>
       </c>
       <c r="AC193" s="3" t="n">
         <v>92026</v>
@@ -23227,7 +23227,7 @@
         <v>1815</v>
       </c>
       <c r="AB194" s="3" t="n">
-        <v>0</v>
+        <v>529</v>
       </c>
       <c r="AC194" s="3" t="n">
         <v>68724</v>
@@ -23337,7 +23337,7 @@
         <v>2189</v>
       </c>
       <c r="AB195" s="3" t="n">
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="AC195" s="3" t="n">
         <v>56642</v>
@@ -23447,7 +23447,7 @@
         <v>3241</v>
       </c>
       <c r="AB196" s="3" t="n">
-        <v>0</v>
+        <v>652</v>
       </c>
       <c r="AC196" s="3" t="n">
         <v>51170</v>
@@ -23557,7 +23557,7 @@
         <v>484</v>
       </c>
       <c r="AB197" s="3" t="n">
-        <v>0</v>
+        <v>1284</v>
       </c>
       <c r="AC197" s="3" t="n">
         <v>43733</v>
@@ -23661,13 +23661,13 @@
         <v>0</v>
       </c>
       <c r="Z198" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA198" s="3" t="n">
         <v>1446</v>
       </c>
       <c r="AB198" s="3" t="n">
-        <v>0</v>
+        <v>692</v>
       </c>
       <c r="AC198" s="3" t="n">
         <v>70658</v>
@@ -23777,7 +23777,7 @@
         <v>780</v>
       </c>
       <c r="AB199" s="3" t="n">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="AC199" s="3" t="n">
         <v>65338</v>
@@ -23887,7 +23887,7 @@
         <v>3840</v>
       </c>
       <c r="AB200" s="3" t="n">
-        <v>0</v>
+        <v>4049</v>
       </c>
       <c r="AC200" s="3" t="n">
         <v>79248</v>
@@ -23997,7 +23997,7 @@
         <v>1550</v>
       </c>
       <c r="AB201" s="3" t="n">
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="AC201" s="3" t="n">
         <v>128199</v>
@@ -24101,13 +24101,13 @@
         <v>-0</v>
       </c>
       <c r="Z202" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA202" s="3" t="n">
         <v>1086</v>
       </c>
       <c r="AB202" s="3" t="n">
-        <v>0</v>
+        <v>766</v>
       </c>
       <c r="AC202" s="3" t="n">
         <v>74745</v>
@@ -24211,13 +24211,13 @@
         <v>0</v>
       </c>
       <c r="Z203" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA203" s="3" t="n">
         <v>1654</v>
       </c>
       <c r="AB203" s="3" t="n">
-        <v>0</v>
+        <v>951</v>
       </c>
       <c r="AC203" s="3" t="n">
         <v>66487</v>
@@ -24327,7 +24327,7 @@
         <v>5512</v>
       </c>
       <c r="AB204" s="3" t="n">
-        <v>0</v>
+        <v>3394</v>
       </c>
       <c r="AC204" s="3" t="n">
         <v>73611</v>
@@ -24431,13 +24431,13 @@
         <v>0</v>
       </c>
       <c r="Z205" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA205" s="3" t="n">
         <v>952</v>
       </c>
       <c r="AB205" s="3" t="n">
-        <v>0</v>
+        <v>1489</v>
       </c>
       <c r="AC205" s="3" t="n">
         <v>91933</v>
@@ -24547,7 +24547,7 @@
         <v>1846</v>
       </c>
       <c r="AB206" s="3" t="n">
-        <v>0</v>
+        <v>928</v>
       </c>
       <c r="AC206" s="3" t="n">
         <v>75705</v>
@@ -24651,13 +24651,13 @@
         <v>0</v>
       </c>
       <c r="Z207" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA207" s="3" t="n">
         <v>1057</v>
       </c>
       <c r="AB207" s="3" t="n">
-        <v>0</v>
+        <v>545</v>
       </c>
       <c r="AC207" s="3" t="n">
         <v>88701</v>
@@ -24767,7 +24767,7 @@
         <v>3110</v>
       </c>
       <c r="AB208" s="3" t="n">
-        <v>0</v>
+        <v>938</v>
       </c>
       <c r="AC208" s="3" t="n">
         <v>34605</v>
@@ -24868,7 +24868,7 @@
         <v>0.001927</v>
       </c>
       <c r="Y209" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z209" s="3" t="n">
         <v>-0</v>
@@ -24877,7 +24877,7 @@
         <v>1413</v>
       </c>
       <c r="AB209" s="3" t="n">
-        <v>0</v>
+        <v>1065</v>
       </c>
       <c r="AC209" s="3" t="n">
         <v>70248</v>
@@ -24987,7 +24987,7 @@
         <v>855</v>
       </c>
       <c r="AB210" s="3" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="AC210" s="3" t="n">
         <v>54199</v>
@@ -25097,7 +25097,7 @@
         <v>1359</v>
       </c>
       <c r="AB211" s="3" t="n">
-        <v>0</v>
+        <v>455</v>
       </c>
       <c r="AC211" s="3" t="n">
         <v>63555</v>
@@ -25207,7 +25207,7 @@
         <v>3507</v>
       </c>
       <c r="AB212" s="3" t="n">
-        <v>0</v>
+        <v>1052</v>
       </c>
       <c r="AC212" s="3" t="n">
         <v>71665</v>
@@ -25311,13 +25311,13 @@
         <v>0</v>
       </c>
       <c r="Z213" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA213" s="3" t="n">
         <v>3049</v>
       </c>
       <c r="AB213" s="3" t="n">
-        <v>0</v>
+        <v>1011</v>
       </c>
       <c r="AC213" s="3" t="n">
         <v>68367</v>
@@ -25427,7 +25427,7 @@
         <v>720</v>
       </c>
       <c r="AB214" s="3" t="n">
-        <v>0</v>
+        <v>1095</v>
       </c>
       <c r="AC214" s="3" t="n">
         <v>84567</v>
@@ -25537,7 +25537,7 @@
         <v>2159</v>
       </c>
       <c r="AB215" s="3" t="n">
-        <v>0</v>
+        <v>606</v>
       </c>
       <c r="AC215" s="3" t="n">
         <v>69673</v>
@@ -25638,7 +25638,7 @@
         <v>0.002042</v>
       </c>
       <c r="Y216" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z216" s="3" t="n">
         <v>0</v>
@@ -25647,7 +25647,7 @@
         <v>1816</v>
       </c>
       <c r="AB216" s="3" t="n">
-        <v>0</v>
+        <v>1221</v>
       </c>
       <c r="AC216" s="3" t="n">
         <v>63703</v>
@@ -25757,7 +25757,7 @@
         <v>572</v>
       </c>
       <c r="AB217" s="3" t="n">
-        <v>0</v>
+        <v>2789</v>
       </c>
       <c r="AC217" s="3" t="n">
         <v>43709</v>
@@ -25858,7 +25858,7 @@
         <v>0.001997</v>
       </c>
       <c r="Y218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z218" s="3" t="n">
         <v>-0</v>
@@ -25867,7 +25867,7 @@
         <v>1537</v>
       </c>
       <c r="AB218" s="3" t="n">
-        <v>0</v>
+        <v>1084</v>
       </c>
       <c r="AC218" s="3" t="n">
         <v>97317</v>
@@ -25977,7 +25977,7 @@
         <v>759</v>
       </c>
       <c r="AB219" s="3" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="AC219" s="3" t="n">
         <v>58675</v>
@@ -26081,13 +26081,13 @@
         <v>0</v>
       </c>
       <c r="Z220" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA220" s="3" t="n">
         <v>2672</v>
       </c>
       <c r="AB220" s="3" t="n">
-        <v>0</v>
+        <v>927</v>
       </c>
       <c r="AC220" s="3" t="n">
         <v>53387</v>
@@ -26197,7 +26197,7 @@
         <v>870</v>
       </c>
       <c r="AB221" s="3" t="n">
-        <v>0</v>
+        <v>1509</v>
       </c>
       <c r="AC221" s="3" t="n">
         <v>104437</v>
@@ -26307,7 +26307,7 @@
         <v>535</v>
       </c>
       <c r="AB222" s="3" t="n">
-        <v>0</v>
+        <v>1768</v>
       </c>
       <c r="AC222" s="3" t="n">
         <v>68283</v>
@@ -26408,7 +26408,7 @@
         <v>0.001956</v>
       </c>
       <c r="Y223" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z223" s="3" t="n">
         <v>-0</v>
@@ -26417,7 +26417,7 @@
         <v>2206</v>
       </c>
       <c r="AB223" s="3" t="n">
-        <v>0</v>
+        <v>920</v>
       </c>
       <c r="AC223" s="3" t="n">
         <v>62984</v>
@@ -26527,7 +26527,7 @@
         <v>1743</v>
       </c>
       <c r="AB224" s="3" t="n">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="AC224" s="3" t="n">
         <v>82993</v>
@@ -26631,13 +26631,13 @@
         <v>0</v>
       </c>
       <c r="Z225" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA225" s="3" t="n">
         <v>981</v>
       </c>
       <c r="AB225" s="3" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="AC225" s="3" t="n">
         <v>75153</v>
@@ -26738,16 +26738,16 @@
         <v>0.001914</v>
       </c>
       <c r="Y226" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z226" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA226" s="3" t="n">
         <v>2347</v>
       </c>
       <c r="AB226" s="3" t="n">
-        <v>0</v>
+        <v>682</v>
       </c>
       <c r="AC226" s="3" t="n">
         <v>64779</v>
@@ -26857,7 +26857,7 @@
         <v>2201</v>
       </c>
       <c r="AB227" s="3" t="n">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="AC227" s="3" t="n">
         <v>62172</v>
@@ -26967,7 +26967,7 @@
         <v>1862</v>
       </c>
       <c r="AB228" s="3" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="AC228" s="3" t="n">
         <v>67491</v>
@@ -27077,7 +27077,7 @@
         <v>2307</v>
       </c>
       <c r="AB229" s="3" t="n">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="AC229" s="3" t="n">
         <v>65546</v>
@@ -27187,7 +27187,7 @@
         <v>2735</v>
       </c>
       <c r="AB230" s="3" t="n">
-        <v>0</v>
+        <v>1637</v>
       </c>
       <c r="AC230" s="3" t="n">
         <v>54773</v>
@@ -27297,7 +27297,7 @@
         <v>1481</v>
       </c>
       <c r="AB231" s="3" t="n">
-        <v>0</v>
+        <v>1297</v>
       </c>
       <c r="AC231" s="3" t="n">
         <v>68993</v>
@@ -27407,7 +27407,7 @@
         <v>1390</v>
       </c>
       <c r="AB232" s="3" t="n">
-        <v>0</v>
+        <v>874</v>
       </c>
       <c r="AC232" s="3" t="n">
         <v>73112</v>
@@ -27517,7 +27517,7 @@
         <v>1699</v>
       </c>
       <c r="AB233" s="3" t="n">
-        <v>0</v>
+        <v>3247</v>
       </c>
       <c r="AC233" s="3" t="n">
         <v>69164</v>
@@ -27627,7 +27627,7 @@
         <v>692</v>
       </c>
       <c r="AB234" s="3" t="n">
-        <v>0</v>
+        <v>1569</v>
       </c>
       <c r="AC234" s="3" t="n">
         <v>78132</v>
@@ -27728,7 +27728,7 @@
         <v>0.001785</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z235" s="3" t="n">
         <v>0</v>
@@ -27737,7 +27737,7 @@
         <v>1929</v>
       </c>
       <c r="AB235" s="3" t="n">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="AC235" s="3" t="n">
         <v>77927</v>
@@ -27847,7 +27847,7 @@
         <v>1275</v>
       </c>
       <c r="AB236" s="3" t="n">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="AC236" s="3" t="n">
         <v>52652</v>
@@ -27957,7 +27957,7 @@
         <v>871</v>
       </c>
       <c r="AB237" s="3" t="n">
-        <v>0</v>
+        <v>639</v>
       </c>
       <c r="AC237" s="3" t="n">
         <v>57626</v>
@@ -28061,13 +28061,13 @@
         <v>0</v>
       </c>
       <c r="Z238" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA238" s="3" t="n">
         <v>2894</v>
       </c>
       <c r="AB238" s="3" t="n">
-        <v>0</v>
+        <v>2815</v>
       </c>
       <c r="AC238" s="3" t="n">
         <v>113705</v>
@@ -28177,7 +28177,7 @@
         <v>1996</v>
       </c>
       <c r="AB239" s="3" t="n">
-        <v>0</v>
+        <v>408</v>
       </c>
       <c r="AC239" s="3" t="n">
         <v>39916</v>
@@ -28278,7 +28278,7 @@
         <v>0.00183</v>
       </c>
       <c r="Y240" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z240" s="3" t="n">
         <v>-0</v>
@@ -28287,7 +28287,7 @@
         <v>1611</v>
       </c>
       <c r="AB240" s="3" t="n">
-        <v>0</v>
+        <v>866</v>
       </c>
       <c r="AC240" s="3" t="n">
         <v>43936</v>
@@ -28397,7 +28397,7 @@
         <v>544</v>
       </c>
       <c r="AB241" s="3" t="n">
-        <v>0</v>
+        <v>1286</v>
       </c>
       <c r="AC241" s="3" t="n">
         <v>71171</v>
@@ -28498,7 +28498,7 @@
         <v>0.001919</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z242" s="3" t="n">
         <v>0</v>
@@ -28507,7 +28507,7 @@
         <v>552</v>
       </c>
       <c r="AB242" s="3" t="n">
-        <v>0</v>
+        <v>1098</v>
       </c>
       <c r="AC242" s="3" t="n">
         <v>66673</v>
@@ -28608,16 +28608,16 @@
         <v>0.001993</v>
       </c>
       <c r="Y243" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z243" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA243" s="3" t="n">
         <v>1212</v>
       </c>
       <c r="AB243" s="3" t="n">
-        <v>0</v>
+        <v>543</v>
       </c>
       <c r="AC243" s="3" t="n">
         <v>61083</v>
@@ -28727,7 +28727,7 @@
         <v>4141</v>
       </c>
       <c r="AB244" s="3" t="n">
-        <v>0</v>
+        <v>605</v>
       </c>
       <c r="AC244" s="3" t="n">
         <v>60110</v>
@@ -28837,7 +28837,7 @@
         <v>2071</v>
       </c>
       <c r="AB245" s="3" t="n">
-        <v>0</v>
+        <v>5690</v>
       </c>
       <c r="AC245" s="3" t="n">
         <v>78384</v>
@@ -28938,16 +28938,16 @@
         <v>0.001896</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z246" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA246" s="3" t="n">
         <v>941</v>
       </c>
       <c r="AB246" s="3" t="n">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="AC246" s="3" t="n">
         <v>61371</v>
@@ -29057,7 +29057,7 @@
         <v>5834</v>
       </c>
       <c r="AB247" s="3" t="n">
-        <v>0</v>
+        <v>2261</v>
       </c>
       <c r="AC247" s="3" t="n">
         <v>33739</v>
@@ -29167,7 +29167,7 @@
         <v>1103</v>
       </c>
       <c r="AB248" s="3" t="n">
-        <v>0</v>
+        <v>543</v>
       </c>
       <c r="AC248" s="3" t="n">
         <v>91621</v>
@@ -29277,7 +29277,7 @@
         <v>1523</v>
       </c>
       <c r="AB249" s="3" t="n">
-        <v>0</v>
+        <v>446</v>
       </c>
       <c r="AC249" s="3" t="n">
         <v>59123</v>
@@ -29387,7 +29387,7 @@
         <v>594</v>
       </c>
       <c r="AB250" s="3" t="n">
-        <v>0</v>
+        <v>961</v>
       </c>
       <c r="AC250" s="3" t="n">
         <v>77155</v>
@@ -29497,7 +29497,7 @@
         <v>348</v>
       </c>
       <c r="AB251" s="3" t="n">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="AC251" s="3" t="n">
         <v>60145</v>
@@ -29601,13 +29601,13 @@
         <v>0</v>
       </c>
       <c r="Z252" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA252" s="3" t="n">
         <v>1672</v>
       </c>
       <c r="AB252" s="3" t="n">
-        <v>0</v>
+        <v>1417</v>
       </c>
       <c r="AC252" s="3" t="n">
         <v>101685</v>
@@ -29717,7 +29717,7 @@
         <v>1538</v>
       </c>
       <c r="AB253" s="3" t="n">
-        <v>0</v>
+        <v>782</v>
       </c>
       <c r="AC253" s="3" t="n">
         <v>55330</v>
@@ -29818,16 +29818,16 @@
         <v>0.001683</v>
       </c>
       <c r="Y254" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z254" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA254" s="3" t="n">
         <v>3118</v>
       </c>
       <c r="AB254" s="3" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="AC254" s="3" t="n">
         <v>83239</v>
@@ -29931,13 +29931,13 @@
         <v>-0</v>
       </c>
       <c r="Z255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA255" s="3" t="n">
         <v>2005</v>
       </c>
       <c r="AB255" s="3" t="n">
-        <v>0</v>
+        <v>609</v>
       </c>
       <c r="AC255" s="3" t="n">
         <v>76021</v>
@@ -30038,16 +30038,16 @@
         <v>0.00163</v>
       </c>
       <c r="Y256" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA256" s="3" t="n">
         <v>2337</v>
       </c>
       <c r="AB256" s="3" t="n">
-        <v>0</v>
+        <v>1167</v>
       </c>
       <c r="AC256" s="3" t="n">
         <v>86970</v>
@@ -30157,7 +30157,7 @@
         <v>1259</v>
       </c>
       <c r="AB257" s="3" t="n">
-        <v>0</v>
+        <v>2935</v>
       </c>
       <c r="AC257" s="3" t="n">
         <v>79497</v>
@@ -30258,16 +30258,16 @@
         <v>0.00168</v>
       </c>
       <c r="Y258" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z258" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA258" s="3" t="n">
         <v>1090</v>
       </c>
       <c r="AB258" s="3" t="n">
-        <v>0</v>
+        <v>1606</v>
       </c>
       <c r="AC258" s="3" t="n">
         <v>55651</v>
@@ -30377,7 +30377,7 @@
         <v>673</v>
       </c>
       <c r="AB259" s="3" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AC259" s="3" t="n">
         <v>59627</v>
@@ -30487,7 +30487,7 @@
         <v>1315</v>
       </c>
       <c r="AB260" s="3" t="n">
-        <v>0</v>
+        <v>1149</v>
       </c>
       <c r="AC260" s="3" t="n">
         <v>64961</v>
@@ -30597,7 +30597,7 @@
         <v>288</v>
       </c>
       <c r="AB261" s="3" t="n">
-        <v>0</v>
+        <v>548</v>
       </c>
       <c r="AC261" s="3" t="n">
         <v>54482</v>
@@ -30707,7 +30707,7 @@
         <v>536</v>
       </c>
       <c r="AB262" s="3" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="AC262" s="3" t="n">
         <v>42983</v>
@@ -30817,7 +30817,7 @@
         <v>745</v>
       </c>
       <c r="AB263" s="3" t="n">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="AC263" s="3" t="n">
         <v>69534</v>
@@ -30927,7 +30927,7 @@
         <v>477</v>
       </c>
       <c r="AB264" s="3" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="AC264" s="3" t="n">
         <v>38005</v>
@@ -31028,16 +31028,16 @@
         <v>0.001646</v>
       </c>
       <c r="Y265" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z265" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA265" s="3" t="n">
         <v>3450</v>
       </c>
       <c r="AB265" s="3" t="n">
-        <v>0</v>
+        <v>826</v>
       </c>
       <c r="AC265" s="3" t="n">
         <v>61636</v>
@@ -31147,7 +31147,7 @@
         <v>3225</v>
       </c>
       <c r="AB266" s="3" t="n">
-        <v>0</v>
+        <v>2383</v>
       </c>
       <c r="AC266" s="3" t="n">
         <v>39538</v>
@@ -31257,7 +31257,7 @@
         <v>867</v>
       </c>
       <c r="AB267" s="3" t="n">
-        <v>0</v>
+        <v>1145</v>
       </c>
       <c r="AC267" s="3" t="n">
         <v>59025</v>
@@ -31361,13 +31361,13 @@
         <v>0</v>
       </c>
       <c r="Z268" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA268" s="3" t="n">
         <v>1537</v>
       </c>
       <c r="AB268" s="3" t="n">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="AC268" s="3" t="n">
         <v>62179</v>
@@ -31467,7 +31467,7 @@
         <v>840</v>
       </c>
       <c r="AB269" s="3" t="n">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="AC269" s="3" t="n">
         <v>36979</v>
@@ -31567,7 +31567,7 @@
         <v>1789</v>
       </c>
       <c r="AB270" s="3" t="n">
-        <v>0</v>
+        <v>1032</v>
       </c>
       <c r="AC270" s="3" t="n">
         <v>60443</v>
@@ -31667,7 +31667,7 @@
         <v>887</v>
       </c>
       <c r="AB271" s="3" t="n">
-        <v>0</v>
+        <v>577</v>
       </c>
       <c r="AC271" s="3" t="n">
         <v>46558</v>
@@ -31767,7 +31767,7 @@
         <v>1174</v>
       </c>
       <c r="AB272" s="3" t="n">
-        <v>0</v>
+        <v>1097</v>
       </c>
       <c r="AC272" s="3" t="n">
         <v>70693</v>
@@ -31867,7 +31867,7 @@
         <v>489</v>
       </c>
       <c r="AB273" s="3" t="n">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="AC273" s="3" t="n">
         <v>57213</v>
@@ -31967,7 +31967,7 @@
         <v>1359</v>
       </c>
       <c r="AB274" s="3" t="n">
-        <v>0</v>
+        <v>3351</v>
       </c>
       <c r="AC274" s="3" t="n">
         <v>44505</v>
@@ -32067,7 +32067,7 @@
         <v>1931</v>
       </c>
       <c r="AB275" s="3" t="n">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="AC275" s="3" t="n">
         <v>40995</v>
@@ -32167,7 +32167,7 @@
         <v>2294</v>
       </c>
       <c r="AB276" s="3" t="n">
-        <v>0</v>
+        <v>1043</v>
       </c>
       <c r="AC276" s="3" t="n">
         <v>82908</v>
@@ -32267,7 +32267,7 @@
         <v>2918</v>
       </c>
       <c r="AB277" s="3" t="n">
-        <v>0</v>
+        <v>2975</v>
       </c>
       <c r="AC277" s="3" t="n">
         <v>47026</v>
@@ -32358,16 +32358,16 @@
         <v>0.001623</v>
       </c>
       <c r="Y278" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z278" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA278" s="3" t="n">
         <v>1102</v>
       </c>
       <c r="AB278" s="3" t="n">
-        <v>0</v>
+        <v>635</v>
       </c>
       <c r="AC278" s="3" t="n">
         <v>67633</v>
@@ -32461,13 +32461,13 @@
         <v>0</v>
       </c>
       <c r="Z279" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA279" s="3" t="n">
         <v>689</v>
       </c>
       <c r="AB279" s="3" t="n">
-        <v>0</v>
+        <v>1609</v>
       </c>
       <c r="AC279" s="3" t="n">
         <v>87906</v>
@@ -32567,7 +32567,7 @@
         <v>4625</v>
       </c>
       <c r="AB280" s="3" t="n">
-        <v>0</v>
+        <v>2269</v>
       </c>
       <c r="AC280" s="3" t="n">
         <v>99588</v>
@@ -32658,16 +32658,16 @@
         <v>0.001582</v>
       </c>
       <c r="Y281" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z281" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA281" s="3" t="n">
         <v>1622</v>
       </c>
       <c r="AB281" s="3" t="n">
-        <v>0</v>
+        <v>1158</v>
       </c>
       <c r="AC281" s="3" t="n">
         <v>72098</v>
@@ -32767,7 +32767,7 @@
         <v>999</v>
       </c>
       <c r="AB282" s="3" t="n">
-        <v>0</v>
+        <v>415</v>
       </c>
       <c r="AC282" s="3" t="n">
         <v>55367</v>
@@ -32867,7 +32867,7 @@
         <v>743</v>
       </c>
       <c r="AB283" s="3" t="n">
-        <v>0</v>
+        <v>1203</v>
       </c>
       <c r="AC283" s="3" t="n">
         <v>80946</v>
@@ -32967,7 +32967,7 @@
         <v>902</v>
       </c>
       <c r="AB284" s="3" t="n">
-        <v>0</v>
+        <v>1273</v>
       </c>
       <c r="AC284" s="3" t="n">
         <v>88163</v>
@@ -33067,7 +33067,7 @@
         <v>497</v>
       </c>
       <c r="AB285" s="3" t="n">
-        <v>0</v>
+        <v>728</v>
       </c>
       <c r="AC285" s="3" t="n">
         <v>63750</v>
@@ -33167,7 +33167,7 @@
         <v>841</v>
       </c>
       <c r="AB286" s="3" t="n">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="AC286" s="3" t="n">
         <v>68874</v>
@@ -33267,7 +33267,7 @@
         <v>1960</v>
       </c>
       <c r="AB287" s="3" t="n">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="AC287" s="3" t="n">
         <v>39909</v>
@@ -33367,7 +33367,7 @@
         <v>1615</v>
       </c>
       <c r="AB288" s="3" t="n">
-        <v>0</v>
+        <v>547</v>
       </c>
       <c r="AC288" s="3" t="n">
         <v>52585</v>
@@ -33467,7 +33467,7 @@
         <v>313</v>
       </c>
       <c r="AB289" s="3" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="AC289" s="3" t="n">
         <v>65922</v>
@@ -33567,7 +33567,7 @@
         <v>1466</v>
       </c>
       <c r="AB290" s="3" t="n">
-        <v>0</v>
+        <v>1484</v>
       </c>
       <c r="AC290" s="3" t="n">
         <v>38083</v>
@@ -33667,7 +33667,7 @@
         <v>3713</v>
       </c>
       <c r="AB291" s="3" t="n">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="AC291" s="3" t="n">
         <v>42174</v>
@@ -33767,7 +33767,7 @@
         <v>786</v>
       </c>
       <c r="AB292" s="3" t="n">
-        <v>0</v>
+        <v>1339</v>
       </c>
       <c r="AC292" s="3" t="n">
         <v>52905</v>
@@ -33867,7 +33867,7 @@
         <v>3348</v>
       </c>
       <c r="AB293" s="3" t="n">
-        <v>0</v>
+        <v>3743</v>
       </c>
       <c r="AC293" s="3" t="n">
         <v>86029</v>
@@ -33967,7 +33967,7 @@
         <v>572</v>
       </c>
       <c r="AB294" s="3" t="n">
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="AC294" s="3" t="n">
         <v>56996</v>
@@ -34061,13 +34061,13 @@
         <v>0</v>
       </c>
       <c r="Z295" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA295" s="3" t="n">
         <v>2825</v>
       </c>
       <c r="AB295" s="3" t="n">
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="AC295" s="3" t="n">
         <v>43582</v>
@@ -34158,16 +34158,16 @@
         <v>0.001619</v>
       </c>
       <c r="Y296" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z296" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA296" s="3" t="n">
         <v>916</v>
       </c>
       <c r="AB296" s="3" t="n">
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="AC296" s="3" t="n">
         <v>47987</v>
@@ -34267,7 +34267,7 @@
         <v>521</v>
       </c>
       <c r="AB297" s="3" t="n">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="AC297" s="3" t="n">
         <v>69396</v>
@@ -34367,7 +34367,7 @@
         <v>627</v>
       </c>
       <c r="AB298" s="3" t="n">
-        <v>0</v>
+        <v>784</v>
       </c>
       <c r="AC298" s="3" t="n">
         <v>48014</v>
@@ -34467,7 +34467,7 @@
         <v>1436</v>
       </c>
       <c r="AB299" s="3" t="n">
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="AC299" s="3" t="n">
         <v>47848</v>
@@ -34567,7 +34567,7 @@
         <v>1455</v>
       </c>
       <c r="AB300" s="3" t="n">
-        <v>0</v>
+        <v>3562</v>
       </c>
       <c r="AC300" s="3" t="n">
         <v>40510</v>
@@ -34658,16 +34658,16 @@
         <v>0.001586</v>
       </c>
       <c r="Y301" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z301" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA301" s="3" t="n">
         <v>1482</v>
       </c>
       <c r="AB301" s="3" t="n">
-        <v>0</v>
+        <v>1048</v>
       </c>
       <c r="AC301" s="3" t="n">
         <v>41421</v>
@@ -34767,7 +34767,7 @@
         <v>6019</v>
       </c>
       <c r="AB302" s="3" t="n">
-        <v>0</v>
+        <v>3266</v>
       </c>
       <c r="AC302" s="3" t="n">
         <v>54909</v>
@@ -34867,7 +34867,7 @@
         <v>1844</v>
       </c>
       <c r="AB303" s="3" t="n">
-        <v>0</v>
+        <v>956</v>
       </c>
       <c r="AC303" s="3" t="n">
         <v>45222</v>
@@ -34958,16 +34958,16 @@
         <v>0.001488</v>
       </c>
       <c r="Y304" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA304" s="3" t="n">
         <v>800</v>
       </c>
       <c r="AB304" s="3" t="n">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="AC304" s="3" t="n">
         <v>55623</v>
@@ -35067,7 +35067,7 @@
         <v>346</v>
       </c>
       <c r="AB305" s="3" t="n">
-        <v>0</v>
+        <v>2675</v>
       </c>
       <c r="AC305" s="3" t="n">
         <v>48721</v>
@@ -35167,7 +35167,7 @@
         <v>1358</v>
       </c>
       <c r="AB306" s="3" t="n">
-        <v>0</v>
+        <v>1770</v>
       </c>
       <c r="AC306" s="3" t="n">
         <v>46334</v>
@@ -35267,7 +35267,7 @@
         <v>1829</v>
       </c>
       <c r="AB307" s="3" t="n">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="AC307" s="3" t="n">
         <v>77339</v>
@@ -35367,7 +35367,7 @@
         <v>404</v>
       </c>
       <c r="AB308" s="3" t="n">
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="AC308" s="3" t="n">
         <v>47175</v>
@@ -35461,13 +35461,13 @@
         <v>0</v>
       </c>
       <c r="Z309" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA309" s="3" t="n">
         <v>1535</v>
       </c>
       <c r="AB309" s="3" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="AC309" s="3" t="n">
         <v>59415</v>
@@ -35567,7 +35567,7 @@
         <v>778</v>
       </c>
       <c r="AB310" s="3" t="n">
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="AC310" s="3" t="n">
         <v>52021</v>
@@ -35658,7 +35658,7 @@
         <v>0.001535</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z311" s="3" t="n">
         <v>-0</v>
@@ -35667,7 +35667,7 @@
         <v>2054</v>
       </c>
       <c r="AB311" s="3" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="AC311" s="3" t="n">
         <v>53750</v>
@@ -35767,7 +35767,7 @@
         <v>3008</v>
       </c>
       <c r="AB312" s="3" t="n">
-        <v>0</v>
+        <v>1591</v>
       </c>
       <c r="AC312" s="3" t="n">
         <v>95059</v>
@@ -35867,7 +35867,7 @@
         <v>627</v>
       </c>
       <c r="AB313" s="3" t="n">
-        <v>0</v>
+        <v>531</v>
       </c>
       <c r="AC313" s="3" t="n">
         <v>51097</v>
@@ -35967,7 +35967,7 @@
         <v>1923</v>
       </c>
       <c r="AB314" s="3" t="n">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="AC314" s="3" t="n">
         <v>52529</v>
@@ -36067,7 +36067,7 @@
         <v>941</v>
       </c>
       <c r="AB315" s="3" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="AC315" s="3" t="n">
         <v>45453</v>
@@ -36167,7 +36167,7 @@
         <v>877</v>
       </c>
       <c r="AB316" s="3" t="n">
-        <v>0</v>
+        <v>912</v>
       </c>
       <c r="AC316" s="3" t="n">
         <v>41042</v>
@@ -36261,13 +36261,13 @@
         <v>0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>1125</v>
       </c>
       <c r="AB317" s="3" t="n">
-        <v>0</v>
+        <v>749</v>
       </c>
       <c r="AC317" s="3" t="n">
         <v>72720</v>
@@ -36358,7 +36358,7 @@
         <v>0.001396</v>
       </c>
       <c r="Y318" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z318" s="3" t="n">
         <v>-0</v>
@@ -36367,7 +36367,7 @@
         <v>1150</v>
       </c>
       <c r="AB318" s="3" t="n">
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="AC318" s="3" t="n">
         <v>34432</v>
@@ -36467,7 +36467,7 @@
         <v>3558</v>
       </c>
       <c r="AB319" s="3" t="n">
-        <v>0</v>
+        <v>1425</v>
       </c>
       <c r="AC319" s="3" t="n">
         <v>35418</v>
@@ -36567,7 +36567,7 @@
         <v>209</v>
       </c>
       <c r="AB320" s="3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AC320" s="3" t="n">
         <v>29697</v>
@@ -36667,7 +36667,7 @@
         <v>569</v>
       </c>
       <c r="AB321" s="3" t="n">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="AC321" s="3" t="n">
         <v>41715</v>
@@ -36767,7 +36767,7 @@
         <v>481</v>
       </c>
       <c r="AB322" s="3" t="n">
-        <v>0</v>
+        <v>768</v>
       </c>
       <c r="AC322" s="3" t="n">
         <v>56816</v>
@@ -36867,7 +36867,7 @@
         <v>887</v>
       </c>
       <c r="AB323" s="3" t="n">
-        <v>0</v>
+        <v>799</v>
       </c>
       <c r="AC323" s="3" t="n">
         <v>70274</v>
@@ -36967,7 +36967,7 @@
         <v>205</v>
       </c>
       <c r="AB324" s="3" t="n">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="AC324" s="3" t="n">
         <v>33998</v>
@@ -37067,7 +37067,7 @@
         <v>1058</v>
       </c>
       <c r="AB325" s="3" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="AC325" s="3" t="n">
         <v>36599</v>
@@ -37167,7 +37167,7 @@
         <v>669</v>
       </c>
       <c r="AB326" s="3" t="n">
-        <v>0</v>
+        <v>862</v>
       </c>
       <c r="AC326" s="3" t="n">
         <v>58667</v>
@@ -37267,7 +37267,7 @@
         <v>1307</v>
       </c>
       <c r="AB327" s="3" t="n">
-        <v>0</v>
+        <v>2732</v>
       </c>
       <c r="AC327" s="3" t="n">
         <v>82450</v>
@@ -37367,7 +37367,7 @@
         <v>2839</v>
       </c>
       <c r="AB328" s="3" t="n">
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="AC328" s="3" t="n">
         <v>27253</v>
@@ -37467,7 +37467,7 @@
         <v>1348</v>
       </c>
       <c r="AB329" s="3" t="n">
-        <v>0</v>
+        <v>624</v>
       </c>
       <c r="AC329" s="3" t="n">
         <v>80276</v>
@@ -37567,7 +37567,7 @@
         <v>1917</v>
       </c>
       <c r="AB330" s="3" t="n">
-        <v>0</v>
+        <v>2142</v>
       </c>
       <c r="AC330" s="3" t="n">
         <v>85340</v>
@@ -37667,7 +37667,7 @@
         <v>2076</v>
       </c>
       <c r="AB331" s="3" t="n">
-        <v>0</v>
+        <v>1741</v>
       </c>
       <c r="AC331" s="3" t="n">
         <v>71766</v>
@@ -37767,7 +37767,7 @@
         <v>1230</v>
       </c>
       <c r="AB332" s="3" t="n">
-        <v>0</v>
+        <v>2094</v>
       </c>
       <c r="AC332" s="3" t="n">
         <v>54328</v>
@@ -37867,7 +37867,7 @@
         <v>2274</v>
       </c>
       <c r="AB333" s="3" t="n">
-        <v>0</v>
+        <v>2027</v>
       </c>
       <c r="AC333" s="3" t="n">
         <v>30737</v>
@@ -37967,7 +37967,7 @@
         <v>1180</v>
       </c>
       <c r="AB334" s="3" t="n">
-        <v>0</v>
+        <v>841</v>
       </c>
       <c r="AC334" s="3" t="n">
         <v>48434</v>
@@ -38067,7 +38067,7 @@
         <v>1831</v>
       </c>
       <c r="AB335" s="3" t="n">
-        <v>0</v>
+        <v>907</v>
       </c>
       <c r="AC335" s="3" t="n">
         <v>64936</v>
@@ -38167,7 +38167,7 @@
         <v>1613</v>
       </c>
       <c r="AB336" s="3" t="n">
-        <v>0</v>
+        <v>1703</v>
       </c>
       <c r="AC336" s="3" t="n">
         <v>58766</v>
@@ -38267,7 +38267,7 @@
         <v>1523</v>
       </c>
       <c r="AB337" s="3" t="n">
-        <v>0</v>
+        <v>1859</v>
       </c>
       <c r="AC337" s="3" t="n">
         <v>28413</v>
@@ -38358,7 +38358,7 @@
         <v>0.001476</v>
       </c>
       <c r="Y338" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z338" s="3" t="n">
         <v>0</v>
@@ -38367,7 +38367,7 @@
         <v>556</v>
       </c>
       <c r="AB338" s="3" t="n">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="AC338" s="3" t="n">
         <v>39874</v>
@@ -38458,7 +38458,7 @@
         <v>0.00144</v>
       </c>
       <c r="Y339" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z339" s="3" t="n">
         <v>0</v>
@@ -38467,7 +38467,7 @@
         <v>622</v>
       </c>
       <c r="AB339" s="3" t="n">
-        <v>0</v>
+        <v>1349</v>
       </c>
       <c r="AC339" s="3" t="n">
         <v>85402</v>
@@ -38567,7 +38567,7 @@
         <v>955</v>
       </c>
       <c r="AB340" s="3" t="n">
-        <v>0</v>
+        <v>565</v>
       </c>
       <c r="AC340" s="3" t="n">
         <v>54049</v>
@@ -38667,7 +38667,7 @@
         <v>1321</v>
       </c>
       <c r="AB341" s="3" t="n">
-        <v>0</v>
+        <v>1069</v>
       </c>
       <c r="AC341" s="3" t="n">
         <v>39461</v>
@@ -38761,13 +38761,13 @@
         <v>0</v>
       </c>
       <c r="Z342" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA342" s="3" t="n">
         <v>105</v>
       </c>
       <c r="AB342" s="3" t="n">
-        <v>0</v>
+        <v>571</v>
       </c>
       <c r="AC342" s="3" t="n">
         <v>48660</v>
@@ -38867,7 +38867,7 @@
         <v>1854</v>
       </c>
       <c r="AB343" s="3" t="n">
-        <v>0</v>
+        <v>1310</v>
       </c>
       <c r="AC343" s="3" t="n">
         <v>25407</v>
@@ -38967,7 +38967,7 @@
         <v>211</v>
       </c>
       <c r="AB344" s="3" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="AC344" s="3" t="n">
         <v>45993</v>
@@ -39058,7 +39058,7 @@
         <v>0.001345</v>
       </c>
       <c r="Y345" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z345" s="3" t="n">
         <v>-0</v>
@@ -39067,7 +39067,7 @@
         <v>1161</v>
       </c>
       <c r="AB345" s="3" t="n">
-        <v>0</v>
+        <v>551</v>
       </c>
       <c r="AC345" s="3" t="n">
         <v>55682</v>
@@ -39167,7 +39167,7 @@
         <v>1249</v>
       </c>
       <c r="AB346" s="3" t="n">
-        <v>0</v>
+        <v>1391</v>
       </c>
       <c r="AC346" s="3" t="n">
         <v>54650</v>
@@ -39258,16 +39258,16 @@
         <v>0.001302</v>
       </c>
       <c r="Y347" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z347" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA347" s="3" t="n">
         <v>849</v>
       </c>
       <c r="AB347" s="3" t="n">
-        <v>0</v>
+        <v>1257</v>
       </c>
       <c r="AC347" s="3" t="n">
         <v>36336</v>
@@ -39367,7 +39367,7 @@
         <v>716</v>
       </c>
       <c r="AB348" s="3" t="n">
-        <v>0</v>
+        <v>1159</v>
       </c>
       <c r="AC348" s="3" t="n">
         <v>28712</v>
@@ -39458,16 +39458,16 @@
         <v>0.001171</v>
       </c>
       <c r="Y349" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z349" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA349" s="3" t="n">
         <v>953</v>
       </c>
       <c r="AB349" s="3" t="n">
-        <v>0</v>
+        <v>1209</v>
       </c>
       <c r="AC349" s="3" t="n">
         <v>49942</v>
@@ -39567,7 +39567,7 @@
         <v>211</v>
       </c>
       <c r="AB350" s="3" t="n">
-        <v>0</v>
+        <v>565</v>
       </c>
       <c r="AC350" s="3" t="n">
         <v>20661</v>
@@ -39667,7 +39667,7 @@
         <v>3739</v>
       </c>
       <c r="AB351" s="3" t="n">
-        <v>0</v>
+        <v>1637</v>
       </c>
       <c r="AC351" s="3" t="n">
         <v>41701</v>
@@ -39767,7 +39767,7 @@
         <v>696</v>
       </c>
       <c r="AB352" s="3" t="n">
-        <v>0</v>
+        <v>627</v>
       </c>
       <c r="AC352" s="3" t="n">
         <v>40035</v>
@@ -39867,7 +39867,7 @@
         <v>2186</v>
       </c>
       <c r="AB353" s="3" t="n">
-        <v>0</v>
+        <v>1653</v>
       </c>
       <c r="AC353" s="3" t="n">
         <v>27549</v>
@@ -39967,7 +39967,7 @@
         <v>1046</v>
       </c>
       <c r="AB354" s="3" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="AC354" s="3" t="n">
         <v>41700</v>
@@ -40061,13 +40061,13 @@
         <v>0</v>
       </c>
       <c r="Z355" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA355" s="3" t="n">
         <v>651</v>
       </c>
       <c r="AB355" s="3" t="n">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="AC355" s="3" t="n">
         <v>48555</v>
@@ -40167,7 +40167,7 @@
         <v>271</v>
       </c>
       <c r="AB356" s="3" t="n">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="AC356" s="3" t="n">
         <v>53906</v>
@@ -40258,7 +40258,7 @@
         <v>0.001242</v>
       </c>
       <c r="Y357" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z357" s="3" t="n">
         <v>-0</v>
@@ -40267,7 +40267,7 @@
         <v>1209</v>
       </c>
       <c r="AB357" s="3" t="n">
-        <v>0</v>
+        <v>1175</v>
       </c>
       <c r="AC357" s="3" t="n">
         <v>49166</v>
@@ -40367,7 +40367,7 @@
         <v>527</v>
       </c>
       <c r="AB358" s="3" t="n">
-        <v>0</v>
+        <v>963</v>
       </c>
       <c r="AC358" s="3" t="n">
         <v>52987</v>
@@ -40467,7 +40467,7 @@
         <v>3110</v>
       </c>
       <c r="AB359" s="3" t="n">
-        <v>0</v>
+        <v>1687</v>
       </c>
       <c r="AC359" s="3" t="n">
         <v>79585</v>
@@ -40567,7 +40567,7 @@
         <v>2349</v>
       </c>
       <c r="AB360" s="3" t="n">
-        <v>0</v>
+        <v>1055</v>
       </c>
       <c r="AC360" s="3" t="n">
         <v>51041</v>
@@ -40661,13 +40661,13 @@
         <v>0</v>
       </c>
       <c r="Z361" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA361" s="3" t="n">
         <v>708</v>
       </c>
       <c r="AB361" s="3" t="n">
-        <v>0</v>
+        <v>761</v>
       </c>
       <c r="AC361" s="3" t="n">
         <v>40611</v>
@@ -40767,7 +40767,7 @@
         <v>2560</v>
       </c>
       <c r="AB362" s="3" t="n">
-        <v>0</v>
+        <v>3334</v>
       </c>
       <c r="AC362" s="3" t="n">
         <v>42141</v>
@@ -40867,7 +40867,7 @@
         <v>372</v>
       </c>
       <c r="AB363" s="3" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="AC363" s="3" t="n">
         <v>36022</v>
@@ -40961,13 +40961,13 @@
         <v>0</v>
       </c>
       <c r="Z364" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA364" s="3" t="n">
         <v>84</v>
       </c>
       <c r="AB364" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC364" s="3" t="n">
         <v>35343</v>
@@ -41067,7 +41067,7 @@
         <v>3541</v>
       </c>
       <c r="AB365" s="3" t="n">
-        <v>0</v>
+        <v>2267</v>
       </c>
       <c r="AC365" s="3" t="n">
         <v>36088</v>
@@ -41167,7 +41167,7 @@
         <v>783</v>
       </c>
       <c r="AB366" s="3" t="n">
-        <v>0</v>
+        <v>1121</v>
       </c>
       <c r="AC366" s="3" t="n">
         <v>49816</v>
@@ -41267,7 +41267,7 @@
         <v>1466</v>
       </c>
       <c r="AB367" s="3" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="AC367" s="3" t="n">
         <v>23524</v>
@@ -41367,7 +41367,7 @@
         <v>1190</v>
       </c>
       <c r="AB368" s="3" t="n">
-        <v>0</v>
+        <v>1070</v>
       </c>
       <c r="AC368" s="3" t="n">
         <v>28949</v>
@@ -41467,7 +41467,7 @@
         <v>761</v>
       </c>
       <c r="AB369" s="3" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="AC369" s="3" t="n">
         <v>23917</v>
@@ -41567,7 +41567,7 @@
         <v>740</v>
       </c>
       <c r="AB370" s="3" t="n">
-        <v>0</v>
+        <v>1307</v>
       </c>
       <c r="AC370" s="3" t="n">
         <v>42958</v>
@@ -41661,13 +41661,13 @@
         <v>-0</v>
       </c>
       <c r="Z371" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA371" s="3" t="n">
         <v>343</v>
       </c>
       <c r="AB371" s="3" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="AC371" s="3" t="n">
         <v>35423</v>
@@ -41767,7 +41767,7 @@
         <v>1418</v>
       </c>
       <c r="AB372" s="3" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="AC372" s="3" t="n">
         <v>23881</v>
@@ -41867,7 +41867,7 @@
         <v>771</v>
       </c>
       <c r="AB373" s="3" t="n">
-        <v>0</v>
+        <v>1620</v>
       </c>
       <c r="AC373" s="3" t="n">
         <v>37740</v>
@@ -41967,7 +41967,7 @@
         <v>293</v>
       </c>
       <c r="AB374" s="3" t="n">
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="AC374" s="3" t="n">
         <v>32649</v>
@@ -42067,7 +42067,7 @@
         <v>1934</v>
       </c>
       <c r="AB375" s="3" t="n">
-        <v>0</v>
+        <v>1829</v>
       </c>
       <c r="AC375" s="3" t="n">
         <v>52072</v>
@@ -42167,7 +42167,7 @@
         <v>159</v>
       </c>
       <c r="AB376" s="3" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="AC376" s="3" t="n">
         <v>37898</v>
@@ -42267,7 +42267,7 @@
         <v>1235</v>
       </c>
       <c r="AB377" s="3" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="AC377" s="3" t="n">
         <v>20826</v>
@@ -42367,7 +42367,7 @@
         <v>607</v>
       </c>
       <c r="AB378" s="3" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="AC378" s="3" t="n">
         <v>51469</v>
@@ -42461,13 +42461,13 @@
         <v>0</v>
       </c>
       <c r="Z379" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA379" s="3" t="n">
         <v>1642</v>
       </c>
       <c r="AB379" s="3" t="n">
-        <v>0</v>
+        <v>677</v>
       </c>
       <c r="AC379" s="3" t="n">
         <v>36062</v>
@@ -42558,7 +42558,7 @@
         <v>0.001105</v>
       </c>
       <c r="Y380" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z380" s="3" t="n">
         <v>0</v>
@@ -42567,7 +42567,7 @@
         <v>247</v>
       </c>
       <c r="AB380" s="3" t="n">
-        <v>0</v>
+        <v>713</v>
       </c>
       <c r="AC380" s="3" t="n">
         <v>54026</v>
@@ -42667,7 +42667,7 @@
         <v>272</v>
       </c>
       <c r="AB381" s="3" t="n">
-        <v>0</v>
+        <v>303</v>
       </c>
       <c r="AC381" s="3" t="n">
         <v>29349</v>
@@ -42761,13 +42761,13 @@
         <v>-0</v>
       </c>
       <c r="Z382" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA382" s="3" t="n">
         <v>792</v>
       </c>
       <c r="AB382" s="3" t="n">
-        <v>0</v>
+        <v>688</v>
       </c>
       <c r="AC382" s="3" t="n">
         <v>30764</v>
@@ -42858,16 +42858,16 @@
         <v>0.001039</v>
       </c>
       <c r="Y383" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z383" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA383" s="3" t="n">
         <v>242</v>
       </c>
       <c r="AB383" s="3" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="AC383" s="3" t="n">
         <v>21057</v>
@@ -42958,16 +42958,16 @@
         <v>0.001105</v>
       </c>
       <c r="Y384" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z384" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA384" s="3" t="n">
         <v>428</v>
       </c>
       <c r="AB384" s="3" t="n">
-        <v>0</v>
+        <v>323</v>
       </c>
       <c r="AC384" s="3" t="n">
         <v>24297</v>
@@ -43067,7 +43067,7 @@
         <v>451</v>
       </c>
       <c r="AB385" s="3" t="n">
-        <v>0</v>
+        <v>783</v>
       </c>
       <c r="AC385" s="3" t="n">
         <v>32150</v>
@@ -43158,16 +43158,16 @@
         <v>0.0009810000000000001</v>
       </c>
       <c r="Y386" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z386" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA386" s="3" t="n">
         <v>562</v>
       </c>
       <c r="AB386" s="3" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="AC386" s="3" t="n">
         <v>24440</v>
@@ -43267,7 +43267,7 @@
         <v>336</v>
       </c>
       <c r="AB387" s="3" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="AC387" s="3" t="n">
         <v>21752</v>
@@ -43358,16 +43358,16 @@
         <v>0.00098</v>
       </c>
       <c r="Y388" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z388" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z388" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA388" s="3" t="n">
         <v>330</v>
       </c>
       <c r="AB388" s="3" t="n">
-        <v>0</v>
+        <v>353</v>
       </c>
       <c r="AC388" s="3" t="n">
         <v>16300</v>
@@ -43467,7 +43467,7 @@
         <v>380</v>
       </c>
       <c r="AB389" s="3" t="n">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="AC389" s="3" t="n">
         <v>22787</v>
@@ -43558,7 +43558,7 @@
         <v>0.000957</v>
       </c>
       <c r="Y390" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z390" s="3" t="n">
         <v>-0</v>
@@ -43567,7 +43567,7 @@
         <v>1161</v>
       </c>
       <c r="AB390" s="3" t="n">
-        <v>0</v>
+        <v>556</v>
       </c>
       <c r="AC390" s="3" t="n">
         <v>31327</v>
@@ -43658,7 +43658,7 @@
         <v>0.00102</v>
       </c>
       <c r="Y391" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z391" s="3" t="n">
         <v>-0</v>
@@ -43667,7 +43667,7 @@
         <v>230</v>
       </c>
       <c r="AB391" s="3" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="AC391" s="3" t="n">
         <v>22069</v>
@@ -43758,7 +43758,7 @@
         <v>0.000975</v>
       </c>
       <c r="Y392" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z392" s="3" t="n">
         <v>0</v>
@@ -43767,7 +43767,7 @@
         <v>502</v>
       </c>
       <c r="AB392" s="3" t="n">
-        <v>0</v>
+        <v>304</v>
       </c>
       <c r="AC392" s="3" t="n">
         <v>24122</v>
@@ -43867,7 +43867,7 @@
         <v>447</v>
       </c>
       <c r="AB393" s="3" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="AC393" s="3" t="n">
         <v>13209</v>
@@ -43958,16 +43958,16 @@
         <v>0.001072</v>
       </c>
       <c r="Y394" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z394" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA394" s="3" t="n">
         <v>506</v>
       </c>
       <c r="AB394" s="3" t="n">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="AC394" s="3" t="n">
         <v>20397</v>
@@ -44067,7 +44067,7 @@
         <v>643</v>
       </c>
       <c r="AB395" s="3" t="n">
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="AC395" s="3" t="n">
         <v>29921</v>
@@ -44167,7 +44167,7 @@
         <v>528</v>
       </c>
       <c r="AB396" s="3" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="AC396" s="3" t="n">
         <v>22479</v>
@@ -44267,7 +44267,7 @@
         <v>648</v>
       </c>
       <c r="AB397" s="3" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="AC397" s="3" t="n">
         <v>22037</v>
@@ -44367,7 +44367,7 @@
         <v>247</v>
       </c>
       <c r="AB398" s="3" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="AC398" s="3" t="n">
         <v>22229</v>
@@ -44467,7 +44467,7 @@
         <v>690</v>
       </c>
       <c r="AB399" s="3" t="n">
-        <v>0</v>
+        <v>1531</v>
       </c>
       <c r="AC399" s="3" t="n">
         <v>26404</v>
@@ -44558,16 +44558,16 @@
         <v>0.000806</v>
       </c>
       <c r="Y400" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z400" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA400" s="3" t="n">
         <v>643</v>
       </c>
       <c r="AB400" s="3" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="AC400" s="3" t="n">
         <v>15729</v>
@@ -44667,7 +44667,7 @@
         <v>1387</v>
       </c>
       <c r="AB401" s="3" t="n">
-        <v>0</v>
+        <v>1804</v>
       </c>
       <c r="AC401" s="3" t="n">
         <v>28979</v>
@@ -44692,20 +44692,20 @@
       </c>
       <c r="W402" s="3" t="inlineStr">
         <is>
-          <t>pearson  (*,  EV)</t>
+          <t>pearson  (*,  NV)</t>
         </is>
       </c>
       <c r="X402" s="3" t="n">
-        <v>0.148412</v>
+        <v>0.7063199999999999</v>
       </c>
       <c r="Y402" s="3" t="n">
-        <v>-0.005699</v>
+        <v>0.733924</v>
       </c>
       <c r="Z402" s="3" t="n">
-        <v>-0.005617</v>
+        <v>0.733855</v>
       </c>
       <c r="AB402" s="3" t="n">
-        <v>0.140965</v>
+        <v>0.745987</v>
       </c>
     </row>
     <row r="403">
@@ -44727,20 +44727,20 @@
       </c>
       <c r="W403" s="3" t="inlineStr">
         <is>
-          <t>spearman (*,  EV)</t>
+          <t>spearman (*,  NV)</t>
         </is>
       </c>
       <c r="X403" s="3" t="n">
-        <v>0.160764</v>
+        <v>0.460874</v>
       </c>
       <c r="Y403" s="3" t="n">
-        <v>0.232399</v>
+        <v>0.317588</v>
       </c>
       <c r="Z403" s="3" t="n">
-        <v>0.230312</v>
+        <v>0.308977</v>
       </c>
       <c r="AB403" s="3" t="n">
-        <v>0.176331</v>
+        <v>0.5042720000000001</v>
       </c>
     </row>
     <row r="404">
@@ -44796,10 +44796,10 @@
         <v>0.58377</v>
       </c>
       <c r="Y405" s="3" t="n">
-        <v>0.125935</v>
+        <v>0.113574</v>
       </c>
       <c r="Z405" s="3" t="n">
-        <v>0.119014</v>
+        <v>0.120339</v>
       </c>
       <c r="AA405" s="3" t="n">
         <v>0.613537</v>
@@ -44834,10 +44834,10 @@
         <v>0.810408</v>
       </c>
       <c r="Y407" s="3" t="n">
-        <v>-0.092001</v>
+        <v>-0.071147</v>
       </c>
       <c r="Z407" s="3" t="n">
-        <v>-0.110284</v>
+        <v>-0.068707</v>
       </c>
       <c r="AC407" s="3" t="n">
         <v>0.872384</v>
@@ -44866,7 +44866,7 @@
       </c>
       <c r="AB408" s="1" t="inlineStr">
         <is>
-          <t>ev cases</t>
+          <t>nv cases</t>
         </is>
       </c>
       <c r="AC408" s="1" t="inlineStr">
@@ -44979,26 +44979,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.140965</v>
+        <v>0.745987</v>
       </c>
       <c r="D3" t="n">
-        <v>0.176331</v>
+        <v>0.5042720000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.143459</v>
+        <v>0.351779</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5673758865248227</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06716417910447761</v>
+        <v>0.5970149253731343</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1241379310344828</v>
+        <v>0.5818181818181819</v>
       </c>
     </row>
     <row r="4">
@@ -45069,26 +45069,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.148412</v>
+        <v>0.7063199999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.160764</v>
+        <v>0.460874</v>
       </c>
       <c r="E6" t="n">
-        <v>0.130657</v>
+        <v>0.318464</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5390070921985816</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05426356589147287</v>
+        <v>0.5891472868217055</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
+        <v>0.5629629629629629</v>
       </c>
     </row>
     <row r="7">
@@ -45136,10 +45136,10 @@
         <v>0.467527</v>
       </c>
       <c r="D8" t="n">
-        <v>0.125935</v>
+        <v>0.113574</v>
       </c>
       <c r="E8" t="n">
-        <v>0.078433</v>
+        <v>0.070838</v>
       </c>
       <c r="F8" t="n">
         <v/>
@@ -45159,17 +45159,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.005699</v>
+        <v>0.733924</v>
       </c>
       <c r="D9" t="n">
-        <v>0.232399</v>
+        <v>0.317588</v>
       </c>
       <c r="E9" t="n">
-        <v>0.190041</v>
+        <v>0.213078</v>
       </c>
       <c r="F9" t="n">
         <v/>
@@ -45196,10 +45196,10 @@
         <v>0.649212</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.092001</v>
+        <v>-0.071147</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.05985</v>
+        <v>-0.045163</v>
       </c>
       <c r="F10" t="n">
         <v/>
@@ -45226,10 +45226,10 @@
         <v>0.467574</v>
       </c>
       <c r="D11" t="n">
-        <v>0.119014</v>
+        <v>0.120339</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07309400000000001</v>
+        <v>0.076026</v>
       </c>
       <c r="F11" t="n">
         <v/>
@@ -45249,17 +45249,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.005617</v>
+        <v>0.733855</v>
       </c>
       <c r="D12" t="n">
-        <v>0.230312</v>
+        <v>0.308977</v>
       </c>
       <c r="E12" t="n">
-        <v>0.188428</v>
+        <v>0.205106</v>
       </c>
       <c r="F12" t="n">
         <v/>
@@ -45286,10 +45286,10 @@
         <v>0.649384</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.110284</v>
+        <v>-0.068707</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.074185</v>
+        <v>-0.043559</v>
       </c>
       <c r="F13" t="n">
         <v/>
@@ -45339,26 +45339,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EV</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.10581</v>
+        <v>0.837454</v>
       </c>
       <c r="D15" t="n">
-        <v>0.191381</v>
+        <v>0.633255</v>
       </c>
       <c r="E15" t="n">
-        <v>0.156261</v>
+        <v>0.459697</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.6312056737588653</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07633587786259542</v>
+        <v>0.6793893129770993</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1408450704225352</v>
+        <v>0.6544117647058824</v>
       </c>
     </row>
     <row r="16">

--- a/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_105.xlsx
+++ b/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_105.xlsx
@@ -859,10 +859,10 @@
         <v>0.019464</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="3" t="n">
         <v>34035</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" s="3" t="n">
         <v>7136</v>
@@ -2428,10 +2428,10 @@
         <v>0.005871</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="n">
         <v>4465</v>
@@ -2548,10 +2548,10 @@
         <v>0.005667</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="n">
         <v>1620</v>
@@ -3028,10 +3028,10 @@
         <v>0.005427</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" s="3" t="n">
         <v>1918</v>
@@ -3508,10 +3508,10 @@
         <v>0.004559</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA23" s="3" t="n">
         <v>4123</v>
@@ -3628,10 +3628,10 @@
         <v>0.005151</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA24" s="3" t="n">
         <v>3006</v>
@@ -3988,7 +3988,7 @@
         <v>0.004224</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>-0</v>
@@ -4708,10 +4708,10 @@
         <v>0.003865</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA33" s="3" t="n">
         <v>11679</v>
@@ -4948,10 +4948,10 @@
         <v>0.004087</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA35" s="3" t="n">
         <v>2538</v>
@@ -5188,10 +5188,10 @@
         <v>0.003682</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="3" t="n">
         <v>2678</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA38" s="3" t="n">
         <v>2893</v>
@@ -6388,7 +6388,7 @@
         <v>0.003516</v>
       </c>
       <c r="Y47" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="3" t="n">
         <v>0</v>
@@ -6628,10 +6628,10 @@
         <v>0.003305</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA49" s="3" t="n">
         <v>7680</v>
@@ -7351,7 +7351,7 @@
         <v>-0</v>
       </c>
       <c r="Z55" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA55" s="3" t="n">
         <v>1293</v>
@@ -7828,7 +7828,7 @@
         <v>0.002932</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z59" s="3" t="n">
         <v>0</v>
@@ -8671,7 +8671,7 @@
         <v>0</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA66" s="3" t="n">
         <v>2524</v>
@@ -8908,7 +8908,7 @@
         <v>0.00306</v>
       </c>
       <c r="Y68" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z68" s="3" t="n">
         <v>0</v>
@@ -9028,10 +9028,10 @@
         <v>0.002994</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA69" s="3" t="n">
         <v>3171</v>
@@ -9991,7 +9991,7 @@
         <v>0</v>
       </c>
       <c r="Z77" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA77" s="3" t="n">
         <v>3194</v>
@@ -10591,7 +10591,7 @@
         <v>0</v>
       </c>
       <c r="Z82" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA82" s="3" t="n">
         <v>3690</v>
@@ -10828,10 +10828,10 @@
         <v>0.002878</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA84" s="3" t="n">
         <v>1745</v>
@@ -10951,7 +10951,7 @@
         <v>0</v>
       </c>
       <c r="Z85" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA85" s="3" t="n">
         <v>765</v>
@@ -11668,10 +11668,10 @@
         <v>0.002422</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="n">
         <v>3818</v>
@@ -12508,10 +12508,10 @@
         <v>0.002646</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>4116</v>
@@ -12988,10 +12988,10 @@
         <v>0.002894</v>
       </c>
       <c r="Y102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z102" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA102" s="3" t="n">
         <v>1151</v>
@@ -13828,10 +13828,10 @@
         <v>0.002646</v>
       </c>
       <c r="Y109" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z109" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA109" s="3" t="n">
         <v>2711</v>
@@ -14191,7 +14191,7 @@
         <v>0</v>
       </c>
       <c r="Z112" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA112" s="3" t="n">
         <v>1092</v>
@@ -14528,7 +14528,7 @@
         <v>0.003037</v>
       </c>
       <c r="Y115" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z115" s="3" t="n">
         <v>0</v>
@@ -14858,10 +14858,10 @@
         <v>0.002517</v>
       </c>
       <c r="Y118" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA118" s="3" t="n">
         <v>4137</v>
@@ -15191,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="Z121" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA121" s="3" t="n">
         <v>2616</v>
@@ -15301,7 +15301,7 @@
         <v>0</v>
       </c>
       <c r="Z122" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA122" s="3" t="n">
         <v>4089</v>
@@ -15851,7 +15851,7 @@
         <v>0</v>
       </c>
       <c r="Z127" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA127" s="3" t="n">
         <v>1776</v>
@@ -16621,7 +16621,7 @@
         <v>0</v>
       </c>
       <c r="Z134" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA134" s="3" t="n">
         <v>5101</v>
@@ -17058,10 +17058,10 @@
         <v>0.002271</v>
       </c>
       <c r="Y138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z138" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA138" s="3" t="n">
         <v>5041</v>
@@ -17168,10 +17168,10 @@
         <v>0.002766</v>
       </c>
       <c r="Y139" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z139" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA139" s="3" t="n">
         <v>1737</v>
@@ -17391,7 +17391,7 @@
         <v>0</v>
       </c>
       <c r="Z141" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA141" s="3" t="n">
         <v>3546</v>
@@ -17498,7 +17498,7 @@
         <v>0.002515</v>
       </c>
       <c r="Y142" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z142" s="3" t="n">
         <v>-0</v>
@@ -18268,10 +18268,10 @@
         <v>0.002226</v>
       </c>
       <c r="Y149" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z149" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA149" s="3" t="n">
         <v>2856</v>
@@ -18488,10 +18488,10 @@
         <v>0.002324</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>1662</v>
@@ -18711,7 +18711,7 @@
         <v>0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>2916</v>
@@ -19038,10 +19038,10 @@
         <v>0.002351</v>
       </c>
       <c r="Y156" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA156" s="3" t="n">
         <v>1967</v>
@@ -19698,7 +19698,7 @@
         <v>0.002359</v>
       </c>
       <c r="Y162" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z162" s="3" t="n">
         <v>0</v>
@@ -20251,7 +20251,7 @@
         <v>0</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA167" s="3" t="n">
         <v>284</v>
@@ -20798,10 +20798,10 @@
         <v>0.002328</v>
       </c>
       <c r="Y172" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z172" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA172" s="3" t="n">
         <v>1267</v>
@@ -20908,7 +20908,7 @@
         <v>0.002336</v>
       </c>
       <c r="Y173" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z173" s="3" t="n">
         <v>0</v>
@@ -21348,10 +21348,10 @@
         <v>0.002421</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>857</v>
@@ -21898,10 +21898,10 @@
         <v>0.002184</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>1727</v>
@@ -22231,7 +22231,7 @@
         <v>0</v>
       </c>
       <c r="Z185" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA185" s="3" t="n">
         <v>1124</v>
@@ -22671,7 +22671,7 @@
         <v>-0</v>
       </c>
       <c r="Z189" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA189" s="3" t="n">
         <v>1846</v>
@@ -23661,7 +23661,7 @@
         <v>0</v>
       </c>
       <c r="Z198" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA198" s="3" t="n">
         <v>1446</v>
@@ -24211,7 +24211,7 @@
         <v>0</v>
       </c>
       <c r="Z203" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA203" s="3" t="n">
         <v>1654</v>
@@ -24431,7 +24431,7 @@
         <v>0</v>
       </c>
       <c r="Z205" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA205" s="3" t="n">
         <v>952</v>
@@ -24871,7 +24871,7 @@
         <v>0</v>
       </c>
       <c r="Z209" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA209" s="3" t="n">
         <v>1413</v>
@@ -25088,7 +25088,7 @@
         <v>0.002032</v>
       </c>
       <c r="Y211" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z211" s="3" t="n">
         <v>-0</v>
@@ -25198,10 +25198,10 @@
         <v>0.001965</v>
       </c>
       <c r="Y212" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z212" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA212" s="3" t="n">
         <v>3507</v>
@@ -25311,7 +25311,7 @@
         <v>0</v>
       </c>
       <c r="Z213" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA213" s="3" t="n">
         <v>3049</v>
@@ -25638,10 +25638,10 @@
         <v>0.002042</v>
       </c>
       <c r="Y216" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z216" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA216" s="3" t="n">
         <v>1816</v>
@@ -25861,7 +25861,7 @@
         <v>0</v>
       </c>
       <c r="Z218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA218" s="3" t="n">
         <v>1537</v>
@@ -26081,7 +26081,7 @@
         <v>0</v>
       </c>
       <c r="Z220" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA220" s="3" t="n">
         <v>2672</v>
@@ -26191,7 +26191,7 @@
         <v>0</v>
       </c>
       <c r="Z221" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA221" s="3" t="n">
         <v>870</v>
@@ -26408,7 +26408,7 @@
         <v>0.001956</v>
       </c>
       <c r="Y223" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z223" s="3" t="n">
         <v>-0</v>
@@ -26738,7 +26738,7 @@
         <v>0.001914</v>
       </c>
       <c r="Y226" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z226" s="3" t="n">
         <v>-0</v>
@@ -27291,7 +27291,7 @@
         <v>-0</v>
       </c>
       <c r="Z231" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA231" s="3" t="n">
         <v>1481</v>
@@ -27401,7 +27401,7 @@
         <v>0</v>
       </c>
       <c r="Z232" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA232" s="3" t="n">
         <v>1390</v>
@@ -27618,10 +27618,10 @@
         <v>0.002001</v>
       </c>
       <c r="Y234" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z234" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA234" s="3" t="n">
         <v>692</v>
@@ -27728,7 +27728,7 @@
         <v>0.001785</v>
       </c>
       <c r="Y235" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z235" s="3" t="n">
         <v>0</v>
@@ -28281,7 +28281,7 @@
         <v>0</v>
       </c>
       <c r="Z240" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA240" s="3" t="n">
         <v>1611</v>
@@ -28498,10 +28498,10 @@
         <v>0.001919</v>
       </c>
       <c r="Y242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z242" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z242" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA242" s="3" t="n">
         <v>552</v>
@@ -28608,10 +28608,10 @@
         <v>0.001993</v>
       </c>
       <c r="Y243" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z243" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA243" s="3" t="n">
         <v>1212</v>
@@ -29268,7 +29268,7 @@
         <v>0.001815</v>
       </c>
       <c r="Y249" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z249" s="3" t="n">
         <v>0</v>
@@ -29818,10 +29818,10 @@
         <v>0.001683</v>
       </c>
       <c r="Y254" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z254" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA254" s="3" t="n">
         <v>3118</v>
@@ -29928,10 +29928,10 @@
         <v>0.001666</v>
       </c>
       <c r="Y255" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z255" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z255" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA255" s="3" t="n">
         <v>2005</v>
@@ -30038,10 +30038,10 @@
         <v>0.00163</v>
       </c>
       <c r="Y256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA256" s="3" t="n">
         <v>2337</v>
@@ -30808,7 +30808,7 @@
         <v>0.001707</v>
       </c>
       <c r="Y263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z263" s="3" t="n">
         <v>-0</v>
@@ -31028,10 +31028,10 @@
         <v>0.001646</v>
       </c>
       <c r="Y265" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z265" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA265" s="3" t="n">
         <v>3450</v>
@@ -31558,10 +31558,10 @@
         <v>0.001717</v>
       </c>
       <c r="Y270" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z270" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA270" s="3" t="n">
         <v>1789</v>
@@ -32358,10 +32358,10 @@
         <v>0.001623</v>
       </c>
       <c r="Y278" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z278" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA278" s="3" t="n">
         <v>1102</v>
@@ -32461,7 +32461,7 @@
         <v>0</v>
       </c>
       <c r="Z279" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA279" s="3" t="n">
         <v>689</v>
@@ -33158,10 +33158,10 @@
         <v>0.001623</v>
       </c>
       <c r="Y286" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>841</v>
@@ -34661,7 +34661,7 @@
         <v>0</v>
       </c>
       <c r="Z301" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA301" s="3" t="n">
         <v>1482</v>
@@ -34861,7 +34861,7 @@
         <v>0</v>
       </c>
       <c r="Z303" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA303" s="3" t="n">
         <v>1844</v>
@@ -34958,7 +34958,7 @@
         <v>0.001488</v>
       </c>
       <c r="Y304" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z304" s="3" t="n">
         <v>-0</v>
@@ -35458,7 +35458,7 @@
         <v>0.001379</v>
       </c>
       <c r="Y309" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z309" s="3" t="n">
         <v>-0</v>
@@ -35658,10 +35658,10 @@
         <v>0.001535</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z311" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA311" s="3" t="n">
         <v>2054</v>
@@ -36361,7 +36361,7 @@
         <v>0</v>
       </c>
       <c r="Z318" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA318" s="3" t="n">
         <v>1150</v>
@@ -36858,10 +36858,10 @@
         <v>0.001561</v>
       </c>
       <c r="Y323" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z323" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA323" s="3" t="n">
         <v>887</v>
@@ -37358,10 +37358,10 @@
         <v>0.001552</v>
       </c>
       <c r="Y328" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z328" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA328" s="3" t="n">
         <v>2839</v>
@@ -38358,10 +38358,10 @@
         <v>0.001476</v>
       </c>
       <c r="Y338" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z338" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA338" s="3" t="n">
         <v>556</v>
@@ -39058,10 +39058,10 @@
         <v>0.001345</v>
       </c>
       <c r="Y345" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z345" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA345" s="3" t="n">
         <v>1161</v>
@@ -39458,7 +39458,7 @@
         <v>0.001171</v>
       </c>
       <c r="Y349" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z349" s="3" t="n">
         <v>-0</v>
@@ -40061,7 +40061,7 @@
         <v>0</v>
       </c>
       <c r="Z355" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA355" s="3" t="n">
         <v>651</v>
@@ -40261,7 +40261,7 @@
         <v>0</v>
       </c>
       <c r="Z357" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA357" s="3" t="n">
         <v>1209</v>
@@ -40658,10 +40658,10 @@
         <v>0.001262</v>
       </c>
       <c r="Y361" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z361" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA361" s="3" t="n">
         <v>708</v>
@@ -40958,10 +40958,10 @@
         <v>0.001378</v>
       </c>
       <c r="Y364" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z364" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA364" s="3" t="n">
         <v>84</v>
@@ -41658,10 +41658,10 @@
         <v>0.001213</v>
       </c>
       <c r="Y371" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z371" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z371" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA371" s="3" t="n">
         <v>343</v>
@@ -42358,10 +42358,10 @@
         <v>0.001156</v>
       </c>
       <c r="Y378" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z378" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA378" s="3" t="n">
         <v>607</v>
@@ -42458,7 +42458,7 @@
         <v>0.000982</v>
       </c>
       <c r="Y379" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z379" s="3" t="n">
         <v>-0</v>
@@ -42958,10 +42958,10 @@
         <v>0.001105</v>
       </c>
       <c r="Y384" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z384" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA384" s="3" t="n">
         <v>428</v>
@@ -43361,7 +43361,7 @@
         <v>0</v>
       </c>
       <c r="Z388" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA388" s="3" t="n">
         <v>330</v>
@@ -43561,7 +43561,7 @@
         <v>0</v>
       </c>
       <c r="Z390" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA390" s="3" t="n">
         <v>1161</v>
@@ -43658,7 +43658,7 @@
         <v>0.00102</v>
       </c>
       <c r="Y391" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z391" s="3" t="n">
         <v>-0</v>
@@ -43958,10 +43958,10 @@
         <v>0.001072</v>
       </c>
       <c r="Y394" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z394" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA394" s="3" t="n">
         <v>506</v>
@@ -44258,10 +44258,10 @@
         <v>0.00096</v>
       </c>
       <c r="Y397" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z397" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA397" s="3" t="n">
         <v>648</v>
@@ -44461,7 +44461,7 @@
         <v>0</v>
       </c>
       <c r="Z399" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA399" s="3" t="n">
         <v>690</v>
@@ -44734,10 +44734,10 @@
         <v>0.460874</v>
       </c>
       <c r="Y403" s="3" t="n">
-        <v>0.317588</v>
+        <v>0.316393</v>
       </c>
       <c r="Z403" s="3" t="n">
-        <v>0.308977</v>
+        <v>0.302127</v>
       </c>
       <c r="AB403" s="3" t="n">
         <v>0.5042720000000001</v>
@@ -44796,10 +44796,10 @@
         <v>0.58377</v>
       </c>
       <c r="Y405" s="3" t="n">
-        <v>0.113574</v>
+        <v>0.143496</v>
       </c>
       <c r="Z405" s="3" t="n">
-        <v>0.120339</v>
+        <v>0.133509</v>
       </c>
       <c r="AA405" s="3" t="n">
         <v>0.613537</v>
@@ -44834,10 +44834,10 @@
         <v>0.810408</v>
       </c>
       <c r="Y407" s="3" t="n">
-        <v>-0.071147</v>
+        <v>-0.059442</v>
       </c>
       <c r="Z407" s="3" t="n">
-        <v>-0.068707</v>
+        <v>-0.077016</v>
       </c>
       <c r="AC407" s="3" t="n">
         <v>0.872384</v>
@@ -45136,10 +45136,10 @@
         <v>0.467527</v>
       </c>
       <c r="D8" t="n">
-        <v>0.113574</v>
+        <v>0.143496</v>
       </c>
       <c r="E8" t="n">
-        <v>0.070838</v>
+        <v>0.09457599999999999</v>
       </c>
       <c r="F8" t="n">
         <v/>
@@ -45166,10 +45166,10 @@
         <v>0.733924</v>
       </c>
       <c r="D9" t="n">
-        <v>0.317588</v>
+        <v>0.316393</v>
       </c>
       <c r="E9" t="n">
-        <v>0.213078</v>
+        <v>0.206911</v>
       </c>
       <c r="F9" t="n">
         <v/>
@@ -45196,10 +45196,10 @@
         <v>0.649212</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.071147</v>
+        <v>-0.059442</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.045163</v>
+        <v>-0.037193</v>
       </c>
       <c r="F10" t="n">
         <v/>
@@ -45226,10 +45226,10 @@
         <v>0.467574</v>
       </c>
       <c r="D11" t="n">
-        <v>0.120339</v>
+        <v>0.133509</v>
       </c>
       <c r="E11" t="n">
-        <v>0.076026</v>
+        <v>0.08730599999999999</v>
       </c>
       <c r="F11" t="n">
         <v/>
@@ -45256,10 +45256,10 @@
         <v>0.733855</v>
       </c>
       <c r="D12" t="n">
-        <v>0.308977</v>
+        <v>0.302127</v>
       </c>
       <c r="E12" t="n">
-        <v>0.205106</v>
+        <v>0.196207</v>
       </c>
       <c r="F12" t="n">
         <v/>
@@ -45286,10 +45286,10 @@
         <v>0.649384</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.068707</v>
+        <v>-0.077016</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.043559</v>
+        <v>-0.050501</v>
       </c>
       <c r="F13" t="n">
         <v/>

--- a/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_105.xlsx
+++ b/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_105.xlsx
@@ -859,10 +859,10 @@
         <v>0.019464</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" s="3" t="n">
         <v>34035</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="3" t="n">
         <v>7136</v>
@@ -2668,10 +2668,10 @@
         <v>0.004953</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="3" t="n">
         <v>4207</v>
@@ -2788,10 +2788,10 @@
         <v>0.004867</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="n">
         <v>6813</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>2380</v>
@@ -3028,10 +3028,10 @@
         <v>0.005427</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="3" t="n">
         <v>1918</v>
@@ -3148,10 +3148,10 @@
         <v>0.004368</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA20" s="3" t="n">
         <v>4952</v>
@@ -3388,10 +3388,10 @@
         <v>0.004167</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA22" s="3" t="n">
         <v>3606</v>
@@ -3508,7 +3508,7 @@
         <v>0.004559</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>-0</v>
@@ -3628,10 +3628,10 @@
         <v>0.005151</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3" t="n">
         <v>3006</v>
@@ -3748,10 +3748,10 @@
         <v>0.004805</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="3" t="n">
         <v>1432</v>
@@ -3991,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA27" s="3" t="n">
         <v>3369</v>
@@ -4348,10 +4348,10 @@
         <v>0.004134</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="3" t="n">
         <v>3860</v>
@@ -4708,10 +4708,10 @@
         <v>0.003865</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA33" s="3" t="n">
         <v>11679</v>
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA37" s="3" t="n">
         <v>2678</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="3" t="n">
         <v>2893</v>
@@ -5548,10 +5548,10 @@
         <v>0.003755</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="3" t="n">
         <v>2060</v>
@@ -6628,7 +6628,7 @@
         <v>0.003305</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="3" t="n">
         <v>-0</v>
@@ -6748,7 +6748,7 @@
         <v>0.00308</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="3" t="n">
         <v>-0</v>
@@ -6991,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA52" s="3" t="n">
         <v>2303</v>
@@ -7348,10 +7348,10 @@
         <v>0.003258</v>
       </c>
       <c r="Y55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z55" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA55" s="3" t="n">
         <v>1293</v>
@@ -7828,10 +7828,10 @@
         <v>0.002932</v>
       </c>
       <c r="Y59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z59" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA59" s="3" t="n">
         <v>2443</v>
@@ -8308,10 +8308,10 @@
         <v>0.003147</v>
       </c>
       <c r="Y63" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z63" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA63" s="3" t="n">
         <v>3557</v>
@@ -8671,7 +8671,7 @@
         <v>0</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA66" s="3" t="n">
         <v>2524</v>
@@ -9511,7 +9511,7 @@
         <v>0</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA73" s="3" t="n">
         <v>1306</v>
@@ -10591,7 +10591,7 @@
         <v>0</v>
       </c>
       <c r="Z82" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA82" s="3" t="n">
         <v>3690</v>
@@ -10831,7 +10831,7 @@
         <v>0</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA84" s="3" t="n">
         <v>1745</v>
@@ -11788,10 +11788,10 @@
         <v>0.002739</v>
       </c>
       <c r="Y92" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z92" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA92" s="3" t="n">
         <v>2843</v>
@@ -12508,10 +12508,10 @@
         <v>0.002646</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>4116</v>
@@ -12991,7 +12991,7 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="n">
         <v>1151</v>
@@ -13711,7 +13711,7 @@
         <v>0</v>
       </c>
       <c r="Z108" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA108" s="3" t="n">
         <v>2304</v>
@@ -13828,10 +13828,10 @@
         <v>0.002646</v>
       </c>
       <c r="Y109" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z109" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA109" s="3" t="n">
         <v>2711</v>
@@ -14418,7 +14418,7 @@
         <v>0.002503</v>
       </c>
       <c r="Y114" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z114" s="3" t="n">
         <v>-0</v>
@@ -14528,7 +14528,7 @@
         <v>0.003037</v>
       </c>
       <c r="Y115" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z115" s="3" t="n">
         <v>0</v>
@@ -14861,7 +14861,7 @@
         <v>-0</v>
       </c>
       <c r="Z118" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA118" s="3" t="n">
         <v>4137</v>
@@ -15851,7 +15851,7 @@
         <v>0</v>
       </c>
       <c r="Z127" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA127" s="3" t="n">
         <v>1776</v>
@@ -17061,7 +17061,7 @@
         <v>0</v>
       </c>
       <c r="Z138" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA138" s="3" t="n">
         <v>5041</v>
@@ -17168,10 +17168,10 @@
         <v>0.002766</v>
       </c>
       <c r="Y139" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z139" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA139" s="3" t="n">
         <v>1737</v>
@@ -17391,7 +17391,7 @@
         <v>0</v>
       </c>
       <c r="Z141" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA141" s="3" t="n">
         <v>3546</v>
@@ -17501,7 +17501,7 @@
         <v>0</v>
       </c>
       <c r="Z142" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA142" s="3" t="n">
         <v>828</v>
@@ -18488,10 +18488,10 @@
         <v>0.002324</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>1662</v>
@@ -18708,10 +18708,10 @@
         <v>0.002399</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>2916</v>
@@ -19808,10 +19808,10 @@
         <v>0.002078</v>
       </c>
       <c r="Y163" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA163" s="3" t="n">
         <v>1844</v>
@@ -20251,7 +20251,7 @@
         <v>0</v>
       </c>
       <c r="Z167" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA167" s="3" t="n">
         <v>284</v>
@@ -20581,7 +20581,7 @@
         <v>0</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA170" s="3" t="n">
         <v>1712</v>
@@ -20908,10 +20908,10 @@
         <v>0.002336</v>
       </c>
       <c r="Y173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z173" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z173" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA173" s="3" t="n">
         <v>1316</v>
@@ -21348,10 +21348,10 @@
         <v>0.002421</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>857</v>
@@ -21458,10 +21458,10 @@
         <v>0.00214</v>
       </c>
       <c r="Y178" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z178" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA178" s="3" t="n">
         <v>1559</v>
@@ -22668,7 +22668,7 @@
         <v>0.002267</v>
       </c>
       <c r="Y189" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z189" s="3" t="n">
         <v>0</v>
@@ -23991,7 +23991,7 @@
         <v>0</v>
       </c>
       <c r="Z201" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA201" s="3" t="n">
         <v>1550</v>
@@ -24538,7 +24538,7 @@
         <v>0.002033</v>
       </c>
       <c r="Y206" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z206" s="3" t="n">
         <v>-0</v>
@@ -24871,7 +24871,7 @@
         <v>0</v>
       </c>
       <c r="Z209" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA209" s="3" t="n">
         <v>1413</v>
@@ -25091,7 +25091,7 @@
         <v>0</v>
       </c>
       <c r="Z211" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA211" s="3" t="n">
         <v>1359</v>
@@ -25198,10 +25198,10 @@
         <v>0.001965</v>
       </c>
       <c r="Y212" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z212" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA212" s="3" t="n">
         <v>3507</v>
@@ -25638,10 +25638,10 @@
         <v>0.002042</v>
       </c>
       <c r="Y216" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z216" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA216" s="3" t="n">
         <v>1816</v>
@@ -25858,10 +25858,10 @@
         <v>0.001997</v>
       </c>
       <c r="Y218" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z218" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA218" s="3" t="n">
         <v>1537</v>
@@ -26191,7 +26191,7 @@
         <v>0</v>
       </c>
       <c r="Z221" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA221" s="3" t="n">
         <v>870</v>
@@ -26408,7 +26408,7 @@
         <v>0.001956</v>
       </c>
       <c r="Y223" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z223" s="3" t="n">
         <v>-0</v>
@@ -27288,10 +27288,10 @@
         <v>0.001953</v>
       </c>
       <c r="Y231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z231" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA231" s="3" t="n">
         <v>1481</v>
@@ -27401,7 +27401,7 @@
         <v>0</v>
       </c>
       <c r="Z232" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA232" s="3" t="n">
         <v>1390</v>
@@ -27618,7 +27618,7 @@
         <v>0.002001</v>
       </c>
       <c r="Y234" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z234" s="3" t="n">
         <v>-0</v>
@@ -28498,7 +28498,7 @@
         <v>0.001919</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z242" s="3" t="n">
         <v>-0</v>
@@ -28611,7 +28611,7 @@
         <v>0</v>
       </c>
       <c r="Z243" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA243" s="3" t="n">
         <v>1212</v>
@@ -29818,10 +29818,10 @@
         <v>0.001683</v>
       </c>
       <c r="Y254" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z254" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA254" s="3" t="n">
         <v>3118</v>
@@ -29928,7 +29928,7 @@
         <v>0.001666</v>
       </c>
       <c r="Y255" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z255" s="3" t="n">
         <v>-0</v>
@@ -30041,7 +30041,7 @@
         <v>0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA256" s="3" t="n">
         <v>2337</v>
@@ -30261,7 +30261,7 @@
         <v>0</v>
       </c>
       <c r="Z258" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA258" s="3" t="n">
         <v>1090</v>
@@ -30811,7 +30811,7 @@
         <v>0</v>
       </c>
       <c r="Z263" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA263" s="3" t="n">
         <v>745</v>
@@ -31028,7 +31028,7 @@
         <v>0.001646</v>
       </c>
       <c r="Y265" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z265" s="3" t="n">
         <v>0</v>
@@ -31558,10 +31558,10 @@
         <v>0.001717</v>
       </c>
       <c r="Y270" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z270" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA270" s="3" t="n">
         <v>1789</v>
@@ -33158,10 +33158,10 @@
         <v>0.001623</v>
       </c>
       <c r="Y286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z286" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA286" s="3" t="n">
         <v>841</v>
@@ -34161,7 +34161,7 @@
         <v>0</v>
       </c>
       <c r="Z296" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA296" s="3" t="n">
         <v>916</v>
@@ -34358,10 +34358,10 @@
         <v>0.001605</v>
       </c>
       <c r="Y298" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z298" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA298" s="3" t="n">
         <v>627</v>
@@ -34661,7 +34661,7 @@
         <v>0</v>
       </c>
       <c r="Z301" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA301" s="3" t="n">
         <v>1482</v>
@@ -34861,7 +34861,7 @@
         <v>0</v>
       </c>
       <c r="Z303" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA303" s="3" t="n">
         <v>1844</v>
@@ -34961,7 +34961,7 @@
         <v>0</v>
       </c>
       <c r="Z304" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA304" s="3" t="n">
         <v>800</v>
@@ -35458,10 +35458,10 @@
         <v>0.001379</v>
       </c>
       <c r="Y309" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z309" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA309" s="3" t="n">
         <v>1535</v>
@@ -35658,10 +35658,10 @@
         <v>0.001535</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z311" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA311" s="3" t="n">
         <v>2054</v>
@@ -36158,10 +36158,10 @@
         <v>0.00142</v>
       </c>
       <c r="Y316" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z316" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA316" s="3" t="n">
         <v>877</v>
@@ -36261,7 +36261,7 @@
         <v>0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>1125</v>
@@ -36358,7 +36358,7 @@
         <v>0.001396</v>
       </c>
       <c r="Y318" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z318" s="3" t="n">
         <v>0</v>
@@ -36758,10 +36758,10 @@
         <v>0.001423</v>
       </c>
       <c r="Y322" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z322" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA322" s="3" t="n">
         <v>481</v>
@@ -36858,10 +36858,10 @@
         <v>0.001561</v>
       </c>
       <c r="Y323" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z323" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA323" s="3" t="n">
         <v>887</v>
@@ -38358,10 +38358,10 @@
         <v>0.001476</v>
       </c>
       <c r="Y338" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z338" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA338" s="3" t="n">
         <v>556</v>
@@ -38461,7 +38461,7 @@
         <v>0</v>
       </c>
       <c r="Z339" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA339" s="3" t="n">
         <v>622</v>
@@ -39258,10 +39258,10 @@
         <v>0.001302</v>
       </c>
       <c r="Y347" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z347" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA347" s="3" t="n">
         <v>849</v>
@@ -39461,7 +39461,7 @@
         <v>0</v>
       </c>
       <c r="Z349" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA349" s="3" t="n">
         <v>953</v>
@@ -40658,10 +40658,10 @@
         <v>0.001262</v>
       </c>
       <c r="Y361" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z361" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA361" s="3" t="n">
         <v>708</v>
@@ -42358,10 +42358,10 @@
         <v>0.001156</v>
       </c>
       <c r="Y378" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z378" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA378" s="3" t="n">
         <v>607</v>
@@ -42458,10 +42458,10 @@
         <v>0.000982</v>
       </c>
       <c r="Y379" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z379" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA379" s="3" t="n">
         <v>1642</v>
@@ -42758,10 +42758,10 @@
         <v>0.00096</v>
       </c>
       <c r="Y382" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z382" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA382" s="3" t="n">
         <v>792</v>
@@ -42958,10 +42958,10 @@
         <v>0.001105</v>
       </c>
       <c r="Y384" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z384" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA384" s="3" t="n">
         <v>428</v>
@@ -43658,10 +43658,10 @@
         <v>0.00102</v>
       </c>
       <c r="Y391" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z391" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA391" s="3" t="n">
         <v>230</v>
@@ -43958,7 +43958,7 @@
         <v>0.001072</v>
       </c>
       <c r="Y394" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z394" s="3" t="n">
         <v>-0</v>
@@ -44258,10 +44258,10 @@
         <v>0.00096</v>
       </c>
       <c r="Y397" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z397" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA397" s="3" t="n">
         <v>648</v>
@@ -44461,7 +44461,7 @@
         <v>0</v>
       </c>
       <c r="Z399" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA399" s="3" t="n">
         <v>690</v>
@@ -44561,7 +44561,7 @@
         <v>0</v>
       </c>
       <c r="Z400" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA400" s="3" t="n">
         <v>643</v>
@@ -44734,10 +44734,10 @@
         <v>0.460874</v>
       </c>
       <c r="Y403" s="3" t="n">
-        <v>0.316393</v>
+        <v>0.320243</v>
       </c>
       <c r="Z403" s="3" t="n">
-        <v>0.302127</v>
+        <v>0.293987</v>
       </c>
       <c r="AB403" s="3" t="n">
         <v>0.5042720000000001</v>
@@ -44796,10 +44796,10 @@
         <v>0.58377</v>
       </c>
       <c r="Y405" s="3" t="n">
-        <v>0.143496</v>
+        <v>0.132816</v>
       </c>
       <c r="Z405" s="3" t="n">
-        <v>0.133509</v>
+        <v>0.135217</v>
       </c>
       <c r="AA405" s="3" t="n">
         <v>0.613537</v>
@@ -44834,10 +44834,10 @@
         <v>0.810408</v>
       </c>
       <c r="Y407" s="3" t="n">
-        <v>-0.059442</v>
+        <v>-0.044483</v>
       </c>
       <c r="Z407" s="3" t="n">
-        <v>-0.077016</v>
+        <v>-0.08744499999999999</v>
       </c>
       <c r="AC407" s="3" t="n">
         <v>0.872384</v>
@@ -45136,10 +45136,10 @@
         <v>0.467527</v>
       </c>
       <c r="D8" t="n">
-        <v>0.143496</v>
+        <v>0.132816</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09457599999999999</v>
+        <v>0.088384</v>
       </c>
       <c r="F8" t="n">
         <v/>
@@ -45166,10 +45166,10 @@
         <v>0.733924</v>
       </c>
       <c r="D9" t="n">
-        <v>0.316393</v>
+        <v>0.320243</v>
       </c>
       <c r="E9" t="n">
-        <v>0.206911</v>
+        <v>0.214056</v>
       </c>
       <c r="F9" t="n">
         <v/>
@@ -45196,10 +45196,10 @@
         <v>0.649212</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.059442</v>
+        <v>-0.044483</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.037193</v>
+        <v>-0.027168</v>
       </c>
       <c r="F10" t="n">
         <v/>
@@ -45226,10 +45226,10 @@
         <v>0.467574</v>
       </c>
       <c r="D11" t="n">
-        <v>0.133509</v>
+        <v>0.135217</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08730599999999999</v>
+        <v>0.08888600000000001</v>
       </c>
       <c r="F11" t="n">
         <v/>
@@ -45256,10 +45256,10 @@
         <v>0.733855</v>
       </c>
       <c r="D12" t="n">
-        <v>0.302127</v>
+        <v>0.293987</v>
       </c>
       <c r="E12" t="n">
-        <v>0.196207</v>
+        <v>0.191996</v>
       </c>
       <c r="F12" t="n">
         <v/>
@@ -45286,10 +45286,10 @@
         <v>0.649384</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.077016</v>
+        <v>-0.08744499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.050501</v>
+        <v>-0.057494</v>
       </c>
       <c r="F13" t="n">
         <v/>

--- a/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_105.xlsx
+++ b/EpiRank_改_Germany/ERA_result_reverse_seqday_d_0.95_loops_105.xlsx
@@ -859,10 +859,10 @@
         <v>0.019464</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="3" t="n">
         <v>34035</v>
@@ -1576,10 +1576,10 @@
         <v>0.009171</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" s="3" t="n">
         <v>8532</v>
@@ -1858,10 +1858,10 @@
         <v>0.007346</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="3" t="n">
         <v>6490</v>
@@ -2428,10 +2428,10 @@
         <v>0.005871</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" s="3" t="n">
         <v>4465</v>
@@ -2668,10 +2668,10 @@
         <v>0.004953</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" s="3" t="n">
         <v>4207</v>
@@ -2788,10 +2788,10 @@
         <v>0.004867</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" s="3" t="n">
         <v>6813</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="3" t="n">
         <v>2380</v>
@@ -3028,10 +3028,10 @@
         <v>0.005427</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" s="3" t="n">
         <v>1918</v>
@@ -3148,10 +3148,10 @@
         <v>0.004368</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3" t="n">
         <v>4952</v>
@@ -3508,7 +3508,7 @@
         <v>0.004559</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>-0</v>
@@ -3748,10 +3748,10 @@
         <v>0.004805</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA25" s="3" t="n">
         <v>1432</v>
@@ -3868,7 +3868,7 @@
         <v>0.003699</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>0</v>
@@ -4351,7 +4351,7 @@
         <v>0</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA30" s="3" t="n">
         <v>3860</v>
@@ -4468,10 +4468,10 @@
         <v>0.004758</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA31" s="3" t="n">
         <v>2551</v>
@@ -4708,7 +4708,7 @@
         <v>0.003865</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="3" t="n">
         <v>-0</v>
@@ -4948,10 +4948,10 @@
         <v>0.004087</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="3" t="n">
         <v>2538</v>
@@ -5671,7 +5671,7 @@
         <v>0</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA41" s="3" t="n">
         <v>1989</v>
@@ -6631,7 +6631,7 @@
         <v>0</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="3" t="n">
         <v>7680</v>
@@ -6748,7 +6748,7 @@
         <v>0.00308</v>
       </c>
       <c r="Y50" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z50" s="3" t="n">
         <v>-0</v>
@@ -6991,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="Z52" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="3" t="n">
         <v>2303</v>
@@ -8671,7 +8671,7 @@
         <v>0</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA66" s="3" t="n">
         <v>2524</v>
@@ -8908,10 +8908,10 @@
         <v>0.00306</v>
       </c>
       <c r="Y68" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA68" s="3" t="n">
         <v>1130</v>
@@ -9511,7 +9511,7 @@
         <v>0</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA73" s="3" t="n">
         <v>1306</v>
@@ -11188,10 +11188,10 @@
         <v>0.003072</v>
       </c>
       <c r="Y87" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z87" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA87" s="3" t="n">
         <v>1472</v>
@@ -11671,7 +11671,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA91" s="3" t="n">
         <v>3818</v>
@@ -12508,10 +12508,10 @@
         <v>0.002646</v>
       </c>
       <c r="Y98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z98" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA98" s="3" t="n">
         <v>4116</v>
@@ -14308,10 +14308,10 @@
         <v>0.002608</v>
       </c>
       <c r="Y113" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z113" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA113" s="3" t="n">
         <v>3508</v>
@@ -14421,7 +14421,7 @@
         <v>0</v>
       </c>
       <c r="Z114" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA114" s="3" t="n">
         <v>1871</v>
@@ -14531,7 +14531,7 @@
         <v>0</v>
       </c>
       <c r="Z115" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA115" s="3" t="n">
         <v>2287</v>
@@ -14638,10 +14638,10 @@
         <v>0.002434</v>
       </c>
       <c r="Y116" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z116" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA116" s="3" t="n">
         <v>1796</v>
@@ -14858,7 +14858,7 @@
         <v>0.002517</v>
       </c>
       <c r="Y118" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z118" s="3" t="n">
         <v>0</v>
@@ -17391,7 +17391,7 @@
         <v>0</v>
       </c>
       <c r="Z141" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA141" s="3" t="n">
         <v>3546</v>
@@ -17501,7 +17501,7 @@
         <v>0</v>
       </c>
       <c r="Z142" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA142" s="3" t="n">
         <v>828</v>
@@ -18488,10 +18488,10 @@
         <v>0.002324</v>
       </c>
       <c r="Y151" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z151" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA151" s="3" t="n">
         <v>1662</v>
@@ -18708,10 +18708,10 @@
         <v>0.002399</v>
       </c>
       <c r="Y153" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z153" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA153" s="3" t="n">
         <v>2916</v>
@@ -19041,7 +19041,7 @@
         <v>0</v>
       </c>
       <c r="Z156" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA156" s="3" t="n">
         <v>1967</v>
@@ -19478,10 +19478,10 @@
         <v>0.001886</v>
       </c>
       <c r="Y160" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z160" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA160" s="3" t="n">
         <v>1626</v>
@@ -19811,7 +19811,7 @@
         <v>0</v>
       </c>
       <c r="Z163" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA163" s="3" t="n">
         <v>1844</v>
@@ -20581,7 +20581,7 @@
         <v>0</v>
       </c>
       <c r="Z170" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA170" s="3" t="n">
         <v>1712</v>
@@ -21128,10 +21128,10 @@
         <v>0.002174</v>
       </c>
       <c r="Y175" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z175" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA175" s="3" t="n">
         <v>1957</v>
@@ -21348,10 +21348,10 @@
         <v>0.002421</v>
       </c>
       <c r="Y177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z177" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA177" s="3" t="n">
         <v>857</v>
@@ -21898,10 +21898,10 @@
         <v>0.002184</v>
       </c>
       <c r="Y182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z182" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA182" s="3" t="n">
         <v>1727</v>
@@ -22011,7 +22011,7 @@
         <v>-0</v>
       </c>
       <c r="Z183" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA183" s="3" t="n">
         <v>1407</v>
@@ -24101,7 +24101,7 @@
         <v>-0</v>
       </c>
       <c r="Z202" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA202" s="3" t="n">
         <v>1086</v>
@@ -24428,7 +24428,7 @@
         <v>0.001952</v>
       </c>
       <c r="Y205" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z205" s="3" t="n">
         <v>-0</v>
@@ -24541,7 +24541,7 @@
         <v>0</v>
       </c>
       <c r="Z206" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA206" s="3" t="n">
         <v>1846</v>
@@ -24871,7 +24871,7 @@
         <v>0</v>
       </c>
       <c r="Z209" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA209" s="3" t="n">
         <v>1413</v>
@@ -25198,7 +25198,7 @@
         <v>0.001965</v>
       </c>
       <c r="Y212" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z212" s="3" t="n">
         <v>-0</v>
@@ -25858,7 +25858,7 @@
         <v>0.001997</v>
       </c>
       <c r="Y218" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z218" s="3" t="n">
         <v>-0</v>
@@ -26188,10 +26188,10 @@
         <v>0.001669</v>
       </c>
       <c r="Y221" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z221" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA221" s="3" t="n">
         <v>870</v>
@@ -26408,7 +26408,7 @@
         <v>0.001956</v>
       </c>
       <c r="Y223" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z223" s="3" t="n">
         <v>-0</v>
@@ -27288,10 +27288,10 @@
         <v>0.001953</v>
       </c>
       <c r="Y231" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z231" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA231" s="3" t="n">
         <v>1481</v>
@@ -28498,10 +28498,10 @@
         <v>0.001919</v>
       </c>
       <c r="Y242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z242" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA242" s="3" t="n">
         <v>552</v>
@@ -28611,7 +28611,7 @@
         <v>0</v>
       </c>
       <c r="Z243" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA243" s="3" t="n">
         <v>1212</v>
@@ -28938,7 +28938,7 @@
         <v>0.001896</v>
       </c>
       <c r="Y246" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z246" s="3" t="n">
         <v>0</v>
@@ -29598,10 +29598,10 @@
         <v>0.001608</v>
       </c>
       <c r="Y252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z252" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA252" s="3" t="n">
         <v>1672</v>
@@ -29928,10 +29928,10 @@
         <v>0.001666</v>
       </c>
       <c r="Y255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z255" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA255" s="3" t="n">
         <v>2005</v>
@@ -30041,7 +30041,7 @@
         <v>0</v>
       </c>
       <c r="Z256" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA256" s="3" t="n">
         <v>2337</v>
@@ -30261,7 +30261,7 @@
         <v>0</v>
       </c>
       <c r="Z258" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA258" s="3" t="n">
         <v>1090</v>
@@ -31028,10 +31028,10 @@
         <v>0.001646</v>
       </c>
       <c r="Y265" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z265" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z265" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA265" s="3" t="n">
         <v>3450</v>
@@ -32661,7 +32661,7 @@
         <v>-0</v>
       </c>
       <c r="Z281" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA281" s="3" t="n">
         <v>1622</v>
@@ -34158,10 +34158,10 @@
         <v>0.001619</v>
       </c>
       <c r="Y296" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z296" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA296" s="3" t="n">
         <v>916</v>
@@ -34358,10 +34358,10 @@
         <v>0.001605</v>
       </c>
       <c r="Y298" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z298" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA298" s="3" t="n">
         <v>627</v>
@@ -34658,10 +34658,10 @@
         <v>0.001586</v>
       </c>
       <c r="Y301" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z301" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA301" s="3" t="n">
         <v>1482</v>
@@ -35461,7 +35461,7 @@
         <v>0</v>
       </c>
       <c r="Z309" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA309" s="3" t="n">
         <v>1535</v>
@@ -35658,7 +35658,7 @@
         <v>0.001535</v>
       </c>
       <c r="Y311" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z311" s="3" t="n">
         <v>-0</v>
@@ -36158,10 +36158,10 @@
         <v>0.00142</v>
       </c>
       <c r="Y316" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z316" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA316" s="3" t="n">
         <v>877</v>
@@ -36261,7 +36261,7 @@
         <v>0</v>
       </c>
       <c r="Z317" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA317" s="3" t="n">
         <v>1125</v>
@@ -36358,10 +36358,10 @@
         <v>0.001396</v>
       </c>
       <c r="Y318" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z318" s="3" t="n">
         <v>-0</v>
-      </c>
-      <c r="Z318" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="AA318" s="3" t="n">
         <v>1150</v>
@@ -36758,10 +36758,10 @@
         <v>0.001423</v>
       </c>
       <c r="Y322" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z322" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA322" s="3" t="n">
         <v>481</v>
@@ -36858,10 +36858,10 @@
         <v>0.001561</v>
       </c>
       <c r="Y323" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z323" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA323" s="3" t="n">
         <v>887</v>
@@ -37358,7 +37358,7 @@
         <v>0.001552</v>
       </c>
       <c r="Y328" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z328" s="3" t="n">
         <v>-0</v>
@@ -38361,7 +38361,7 @@
         <v>0</v>
       </c>
       <c r="Z338" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA338" s="3" t="n">
         <v>556</v>
@@ -39061,7 +39061,7 @@
         <v>0</v>
       </c>
       <c r="Z345" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA345" s="3" t="n">
         <v>1161</v>
@@ -40661,7 +40661,7 @@
         <v>0</v>
       </c>
       <c r="Z361" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA361" s="3" t="n">
         <v>708</v>
@@ -40958,7 +40958,7 @@
         <v>0.001378</v>
       </c>
       <c r="Y364" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z364" s="3" t="n">
         <v>-0</v>
@@ -41661,7 +41661,7 @@
         <v>0</v>
       </c>
       <c r="Z371" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA371" s="3" t="n">
         <v>343</v>
@@ -42361,7 +42361,7 @@
         <v>0</v>
       </c>
       <c r="Z378" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA378" s="3" t="n">
         <v>607</v>
@@ -42561,7 +42561,7 @@
         <v>0</v>
       </c>
       <c r="Z380" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA380" s="3" t="n">
         <v>247</v>
@@ -42858,10 +42858,10 @@
         <v>0.001039</v>
       </c>
       <c r="Y383" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z383" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA383" s="3" t="n">
         <v>242</v>
@@ -43158,10 +43158,10 @@
         <v>0.0009810000000000001</v>
       </c>
       <c r="Y386" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z386" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA386" s="3" t="n">
         <v>562</v>
@@ -43358,10 +43358,10 @@
         <v>0.00098</v>
       </c>
       <c r="Y388" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z388" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA388" s="3" t="n">
         <v>330</v>
@@ -43961,7 +43961,7 @@
         <v>0</v>
       </c>
       <c r="Z394" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA394" s="3" t="n">
         <v>506</v>
@@ -44261,7 +44261,7 @@
         <v>0</v>
       </c>
       <c r="Z397" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA397" s="3" t="n">
         <v>648</v>
@@ -44461,7 +44461,7 @@
         <v>0</v>
       </c>
       <c r="Z399" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA399" s="3" t="n">
         <v>690</v>
@@ -44561,7 +44561,7 @@
         <v>0</v>
       </c>
       <c r="Z400" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA400" s="3" t="n">
         <v>643</v>
@@ -44734,10 +44734,10 @@
         <v>0.460874</v>
       </c>
       <c r="Y403" s="3" t="n">
-        <v>0.320243</v>
+        <v>0.290265</v>
       </c>
       <c r="Z403" s="3" t="n">
-        <v>0.293987</v>
+        <v>0.274927</v>
       </c>
       <c r="AB403" s="3" t="n">
         <v>0.5042720000000001</v>
@@ -44796,10 +44796,10 @@
         <v>0.58377</v>
       </c>
       <c r="Y405" s="3" t="n">
-        <v>0.132816</v>
+        <v>0.141659</v>
       </c>
       <c r="Z405" s="3" t="n">
-        <v>0.135217</v>
+        <v>0.123586</v>
       </c>
       <c r="AA405" s="3" t="n">
         <v>0.613537</v>
@@ -44834,10 +44834,10 @@
         <v>0.810408</v>
       </c>
       <c r="Y407" s="3" t="n">
-        <v>-0.044483</v>
+        <v>-0.08014499999999999</v>
       </c>
       <c r="Z407" s="3" t="n">
-        <v>-0.08744499999999999</v>
+        <v>-0.111145</v>
       </c>
       <c r="AC407" s="3" t="n">
         <v>0.872384</v>
@@ -45136,10 +45136,10 @@
         <v>0.467527</v>
       </c>
       <c r="D8" t="n">
-        <v>0.132816</v>
+        <v>0.141659</v>
       </c>
       <c r="E8" t="n">
-        <v>0.088384</v>
+        <v>0.094024</v>
       </c>
       <c r="F8" t="n">
         <v/>
@@ -45166,10 +45166,10 @@
         <v>0.733924</v>
       </c>
       <c r="D9" t="n">
-        <v>0.320243</v>
+        <v>0.290265</v>
       </c>
       <c r="E9" t="n">
-        <v>0.214056</v>
+        <v>0.188135</v>
       </c>
       <c r="F9" t="n">
         <v/>
@@ -45196,10 +45196,10 @@
         <v>0.649212</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.044483</v>
+        <v>-0.08014499999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.027168</v>
+        <v>-0.052256</v>
       </c>
       <c r="F10" t="n">
         <v/>
@@ -45226,10 +45226,10 @@
         <v>0.467574</v>
       </c>
       <c r="D11" t="n">
-        <v>0.135217</v>
+        <v>0.123586</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08888600000000001</v>
+        <v>0.079761</v>
       </c>
       <c r="F11" t="n">
         <v/>
@@ -45256,10 +45256,10 @@
         <v>0.733855</v>
       </c>
       <c r="D12" t="n">
-        <v>0.293987</v>
+        <v>0.274927</v>
       </c>
       <c r="E12" t="n">
-        <v>0.191996</v>
+        <v>0.175451</v>
       </c>
       <c r="F12" t="n">
         <v/>
@@ -45286,10 +45286,10 @@
         <v>0.649384</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.08744499999999999</v>
+        <v>-0.111145</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.057494</v>
+        <v>-0.074336</v>
       </c>
       <c r="F13" t="n">
         <v/>
